--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -910,7 +910,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Share de-identified sample 835 remits and payer denial letters (or confirm synthetic only).</t>
+          <t>Decide whether real sample 835 remits/denial letters will ever be used (default: synthetic only); if yes, counsel-approved de-identification and an intake path first.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Sample files (no PHI) or confirmation.</t>
+          <t>Decision only. Never commit samples or attach them to this sheet.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Names/contacts of willing practices (no PHI).</t>
+          <t>Pointer to where contacts are kept outside the repo (e.g. CRM); no names here.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -1591,16 +1591,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L21"/>
-  <dataValidations count="6">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"P0,P1,P2,P3"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Data source,Clarification,Decision,Legal/Compliance,Vendor/Account,Design/Brand,Business"</formula1>
-    </dataValidation>
+  <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1589,8 +1589,278 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>OA-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Confirm whether a late appeal submission (past the computed deadline) should be blocked, warned, or only recorded and flagged.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>A1 records and flags; a human should confirm this before A2/A3 lock in stricter behavior.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Decision: block / warn / record-and-flag (current default).</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>specs/appeals.md</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 agent</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Before A2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>OA-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the withdrawn/dismissed decision outcome's mapping to a denial status (A1 default: both set the denial to 'closed' with a required reason).</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>A withdrawal for a procedural reason may need to stay distinguishable from a dismissal on the merits.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Decision to keep the A1 default or add a distinct denial status/flag.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>specs/appeals.md</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 agent</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Before A2/A3</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>OA-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Decide if an appeal needs its own immutable version history (like claim_versions) once A2 adds an editable letter body.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Shapes whether A2 needs a new history table before shipping editable letter content.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no decision.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>specs/appeals.md</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 agent</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Before A2</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>OA-024</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Data source</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Provide a source and an annual-update owner for Medicare appeal amount-in-controversy thresholds (REQUIREMENTS §4.2, QIC/ALJ/Council/federal court).</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>rules/catalog.ts cannot encode the higher Medicare appeal levels' thresholds without a cited source.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Citation/source + who keeps it current.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>specs/appeals.md; rules/</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 agent</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Before A3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>OA-025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Confirm whether any role/field visibility rule beyond the existing claim/denial matrix should mask an appeal's tracking_reference or recovered_cents.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Confirms R-5.1.2 coverage extends correctly to the new appeal fields.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no per field, or 'no change'.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>specs/appeals.md; R-5.1.2</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 agent</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Before A2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L21"/>
+  <autoFilter ref="A1:L26"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1589,8 +1589,116 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>OA-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Confirm (or have a biller/counsel confirm) how each CARC maps to a denial category, and which adjustments count as denials versus expected reductions (DenialDesk treats PR and CO-45 as expected).</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Remittance posting now captures denials automatically; the category drives the work queue and appeal routing.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed CARC → category table (src/domain/carc.ts) and the expected-adjustment list, with source.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>R-3.10.1, specs/remittances-and-prompt-pay.md (R2)</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>agent R2 2026-09-26</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Before real remittances</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>OA-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Confirm how late-payment interest should start (payment due date) and whether it accrues on claims still unpaid.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Prompt-pay interest worksheet and totals depend on it (currently pending counsel verification).</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Counsel answer with citation (§ 627.6131 interest subsection).</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>R-3.1.3, rules/prompt-pay.ts</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>agent R2 2026-09-26</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Before production</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L21"/>
+  <autoFilter ref="A1:L23"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1859,8 +1859,278 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>OA-026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Confirm whether a draft (or in_review/ready) appeal that's never submitted can be abandoned/withdrawn, or must always move to submitted before it can be closed out.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>The A1 status trigger only allows withdrawn/dismissed from submitted or awaiting_decision; an abandoned draft currently has no exit path.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Decision: add a draft-cancel transition, or confirm drafts must always be submitted or left open.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>specs/appeals.md</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 review</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Before A2</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>OA-027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Confirm compliance's read-only role on appeals still permits full member-ID reveal, consistent with (or overriding) the same open question on denials/claims (R-5.1.2).</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Appeals reuse the denial/claim role matrix; an unresolved compliance-visibility decision there also applies here.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Decision: compliance sees masked-only, or full reveal like other roles.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>specs/appeals.md; R-5.1.2</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 review</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Before real data</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>OA-028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Counsel sign-off on the Medicare appeal-level rules added for levels 2-5: the 5-day receipt presumption applied to QIC/ALJ/Council/federal court (not yet confirmed for those levels the way it is for redetermination), the federal-court citation (42 CFR 405.1132 vs 405.1136(c)), and the amount-in-controversy thresholds (42 CFR 405.1006, currently unsourced).</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>All of rules/catalog.ts's levels 2-5 rules are flagged VERIFY; A3 cannot compute a level 2-5 deadline for real practices without this.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed citations/values, or corrections, per rule ID.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>rules/catalog.ts; rules/deadlines.ts</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 review</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Before A3</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>OA-029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Decide whether sensitivity-tag masking (HIV, SUD/Part 2, etc.) should be enforced on the appeal and denial detail pages now, or deferred with the rest of the sensitivity-tag work (R-3.5.1).</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Appeals show the same patient/claim fields as denials, which don't yet enforce sensitivity tags.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Decision: enforce now (adds scope to A2) or defer (tracked with the existing sensitivity-tag gap).</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>specs/appeals.md; R-3.5.1</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 review</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Before real data</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>OA-030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the retention period for appeal records (appeals, appeal_notes) once a real retention policy exists.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>No retention/legal-hold policy is defined yet for the new tables, same gap as claims/denials.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Retention period or pointer to the practice's policy.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>specs/appeals.md</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>appeals A1 review</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Before real data</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:L31"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1697,8 +1697,62 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>OA-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Confirm whether practices need a written handling/retention policy for downloaded Insight .xlsx report exports.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Exported workbooks leave the audited system as files on a user's device; owner said 'not sure, let's confirm' on 2026-09-26.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no decision, and policy text or pointer if yes.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>R-9.2.1, SOC 2 C1.1/CC6.7; specs/insight-standard-reports.md</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>insights-standard-reports session 2026-09-26</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Before broad rollout</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L23"/>
+  <autoFilter ref="A1:L24"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1697,8 +1697,62 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>OA-023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Have Florida healthcare counsel confirm the deadline-computation readings now encoded in rules/: (1) whether Fla. R. Gen. Prac. &amp; Jud. Admin. 2.514 weekend/holiday roll-forward applies to prompt-pay and timely-filing clocks outside court, and which Florida holiday list governs (§ 110.117 vs § 683.01); (2) the meaning of 'month' under Fla. Stat. § 1.01 and end-of-month clamping (Aug 31 + 6 months = Feb 28/29); (3) date of service vs date of discharge as the timely-filing anchor for inpatient claims; (4) that Medicare Advantage is outside Florida prompt pay (plan contract; 42 CFR 422.520 30-day clean-claim rule for non-contracted providers); (5) interest starting the first calendar day after the prompt-pay deadline; (6) Medicare 1-year filing with next-federal-workday roll-forward.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Every computed deadline on the claims, denials and prompt-pay pages depends on these readings; all stay VERIFY until confirmed.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Counsel answer per item with citation; then a human records confirmedBy on each rule.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>R-15.6, R-3.1.1, R-3.1.3, R-3.1.5, R-4.2.1, specs/rules-engine-skeleton.md</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>florida-rules-engine 2026-09-26</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Before production</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L23"/>
+  <autoFilter ref="A1:L24"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Exported workbooks leave the audited system as files on a user's device; owner said 'not sure, let's confirm' on 2026-09-26.</t>
+          <t>Exported workbooks leave the audited system as files on a user's device; owner said 'not sure, let's confirm' on 2026-09-26. GATES PRODUCTION: Insight export must not be enabled for a real (Azure) practice tenant until this is answered (docs/PROJECT_STATE.md).</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Before broad rollout</t>
+          <t>Before enabling Insight export in production (Azure)</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Have Florida healthcare counsel confirm the deadline-computation readings now encoded in rules/: (1) whether Fla. R. Gen. Prac. &amp; Jud. Admin. 2.514 weekend/holiday roll-forward applies to prompt-pay and timely-filing clocks outside court, and which Florida holiday list governs (§ 110.117 vs § 683.01); (2) the meaning of 'month' under Fla. Stat. § 1.01 and end-of-month clamping (Aug 31 + 6 months = Feb 28/29); (3) date of service vs date of discharge as the timely-filing anchor for inpatient claims; (4) that Medicare Advantage is outside Florida prompt pay (plan contract; 42 CFR 422.520 30-day clean-claim rule for non-contracted providers); (5) interest starting the first calendar day after the prompt-pay deadline; (6) Medicare 1-year filing with next-federal-workday roll-forward.</t>
+          <t>Have Florida healthcare counsel confirm the deadline-computation readings now encoded in rules/: (1) whether Fla. R. Gen. Prac. &amp; Jud. Admin. 2.514 weekend/holiday roll-forward applies to prompt-pay and timely-filing clocks outside court, and which Florida holiday list governs (§ 110.117 vs § 683.01); (2) the meaning of 'month' under Fla. Stat. § 1.01 and end-of-month clamping (Aug 31 + 6 months = Feb 28/29); (3) date of service vs date of discharge as the timely-filing anchor for inpatient claims; (4) that Medicare Advantage is outside Florida prompt pay (plan contract; 42 CFR 422.520 30-day clean-claim rule for non-contracted providers); (5) interest starting the first calendar day after the prompt-pay deadline; (6) Medicare 1-year filing with next-federal-workday roll-forward. (7) accept or reject the engineering choice (not an owner decision) to apply the reading attributes anchor, rollForward, side and confirmedBy, and the FL insurer/HMO split, to the baseline rule versions instead of adding new effective-dated versions. Until (1) is confirmed, the owner chose option 1 (2026-09-27): the unrolled date governs for provider-side and payer-side deadlines; the rolled date is shown as 'pending counsel' only. After confirmation a human adds a confirmed version to ROLL_FORWARD_POLICY in rules/roll-forward.ts.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1748,7 +1748,11 @@
           <t>Before production</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27: option 1 chosen (conservative/unrolled date governs until counsel confirms roll-forward).</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2291,8 +2291,62 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>OA-034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Decide whether DenialDesk University lesson completions should serve as HIPAA training evidence for practices, and in what form (per-user table under Settings, .xlsx export).</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Sets the scope of University U3 (practice training record) and whether it counts toward R-10.4.</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no, the practice roles who may see it, and any required fields (e.g. annual re-take).</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>R-10.4; specs/denialdesk-university.md U3</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>university session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Before U3</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L34"/>
+  <autoFilter ref="A1:L35"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2349,8 +2349,62 @@
       </c>
       <c r="L35" s="2" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>OA-035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Decide the structure of the University module beyond the Wiki (courses, role-based tracks, training records for R-10.4, or something else).</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>The Wiki shipped as the University's only page; the rest of the module is deliberately unbuilt until the owner shapes it.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>A short outline of the University's sections and what a practice user should be able to do in each.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/university-wiki.md, R-10.4</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>agent 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Before the next University feature</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L34"/>
+  <autoFilter ref="A1:L36"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="214">
   <si>
     <t>ID</t>
   </si>
@@ -649,13 +649,16 @@
     <t>Review</t>
   </si>
   <si>
-    <t>Native-speaker review of the Spanish and Portuguese billing terminology used across the product (glossary in specs/internationalization.md).</t>
+    <t>Native-speaker review of the Spanish and Portuguese billing terminology (glossary in specs/internationalization.md), plus counsel/compliance sign-off that translated attestations and caveats (synthetic-data attestation, BAA recording labels, uncontestable-obligation alert, R-8.7 suppression and residual-risk text) mean the same thing in law.</t>
   </si>
   <si>
     <t>The agent-authored translations use U.S. Spanish and Brazilian Portuguese billing vocabulary (reclamación / reivindicação, denegación / negativa, apelación / recurso, remesa / remessa). A biller who works in those languages should confirm the terms match what Florida practices actually say before launch.</t>
   </si>
   <si>
     <t>Confirmed or corrected glossary rows; any screen wording to change.</t>
+  </si>
+  <si>
+    <t>Before the Azure (production) launch</t>
   </si>
 </sst>
 </file>
@@ -2230,7 +2233,7 @@
         <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>209</v>
@@ -2251,7 +2254,7 @@
         <v>206</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2457,8 +2457,62 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>OA-037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Design/Brand</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the license and generating tool for the DenialDesk Wiki wordmark (public/brand/denialdesk-wiki.png) and that DenialDesk holds the rights to use the logo mark in it.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>The wordmark is shown in the header on every signed-in screen; its provenance is unrecorded (same open question as the reception image).</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>License/rights confirmation and the tool used, noted in public/brand/README.md.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/university-wiki.md, DESIGN.md §4</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>agent 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L37"/>
+  <autoFilter ref="A1:L38"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -2480,7 +2480,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Confirm the license and generating tool for the DenialDesk Wiki wordmark (public/brand/denialdesk-wiki.png) and that DenialDesk holds the rights to use the logo mark in it.</t>
+          <t>Confirm the license and generating tool for the DenialDesk Wiki wordmark (public/brand/denialdesk-wiki.png) and the University of DenialDesk logo (public/brand/university-of-denialdesk.png), and that DenialDesk holds the rights to use the logo mark in them.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>License/rights confirmation and the tool used, noted in public/brand/README.md.</t>
+          <t>License/rights confirmation and the tool used for each, noted in public/brand/README.md.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>The wordmark is shown in the header on every signed-in screen; its provenance is unrecorded (same open question as the reception image).</t>
+          <t>Both logos are shown in the header on every signed-in screen and on the welcome page; their provenance is unrecorded (same open question as the reception image).</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>docs/specs/university-wiki.md, DESIGN.md §4</t>
+          <t>docs/specs/university-wiki.md, docs/specs/denialdesk-university.md, DESIGN.md §4, public/brand/README.md</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2511,8 +2511,62 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>OA-038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Ask counsel whether calling the training center "University of DenialDesk" / "DenialDesk University" is permitted under Florida rules on the use of "university" in a name (Fla. Stat. ch. 1005, Commission for Independent Education) or needs a different name before launch.</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>The name appears in the app header, welcome page, and user menu; renaming later would touch the logo, copy, and URLs.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Counsel's answer; if a rename is needed, the new name.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>specs/denialdesk-university.md; public/brand/README.md</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>compliance-checker 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L38"/>
+  <autoFilter ref="A1:L39"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -2755,17 +2755,17 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Define the DenialDesk University offer behind the access prompt: what "starting at $299" covers (per practice or per user, term, renewals), the purchase channel that "Request access" should feed (today it only records an audit event), and whether the courses should be locked until a practice has bought access.</t>
+          <t>Define the DenialDesk University offer: what "starting at $299" covers (term, renewals, higher tiers), how a practice pays (today the operator records the purchase by hand on the practice page after a request), and who at DenialDesk watches for access requests.</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>The prompt tells every user access is paid while the courses stay open to everyone; sales follow-up has nowhere to land.</t>
+          <t>Decided 2026-09-27: courses are locked until the operator grants access. Without payment terms and an owner of the request queue, requests can sit unseen and the price shown has no defined scope.</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Pricing terms, a contact or checkout channel, and a gate-or-not decision.</t>
+          <t>Pricing terms, the payment/ordering process, and the person who reviews requests in the console.</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -2770,7 +2770,7 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t>specs/denialdesk-university.md (Access prompt); src/domain/university/offer.ts</t>
+          <t>specs/denialdesk-university.md (Access); src/domain/university/offer.ts</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$44</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2786,8 +2786,62 @@
       <c r="K43" s="3" t="inlineStr"/>
       <c r="L43" s="3" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>OA-044</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Confirm that practice-wide denial totals without identifiers (counts and sums on the home page) are not a PHI read and need no audit event.</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>The home page revamp shows live open-denial totals without auditing each view; Insight reports audit aggregates as PHI-adjacent, so the rule should be set once.</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no; if no, the agent adds an audit event to the home page strip.</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>R-7.5.1; specs/welcome-page.md</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>home-page revamp session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>Before the Azure (production) launch</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L43"/>
+  <autoFilter ref="A1:L44"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$56</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2840,8 +2840,656 @@
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>OA-045</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Decide with counsel whether an administrator's U.S.-hosting attestation for the practice's EHR endpoint is enough, or whether DenialDesk must get written confirmation from the EHR vendor; confirm the customer BAA covers DenialDesk pulling patient data from the practice's EHR.</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Fla. Stat. § 408.051(3) data residency and the BAA scope gate every real EHR connection.</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Counsel answer: attestation vs. vendor letter, and BAA wording if a change is needed.</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-045); R-3.3.1</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>OA-046</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether to retire manual patient registration once a practice's EHR is connected, and what happens to older manually entered patients that never match a synced record.</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>The owner asked that DenialDesk sync patients rather than hold them; manual entry is kept only for practices without a connection.</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no on retiring manual registration, plus the rule for unmatched manual patients (stay read-only, archive, or editable).</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-046)</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>Before PI3</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>OA-047</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Confirm that patient phone and email are not synced from the EHR (billing minimum only).</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Minimum necessary (R-5.1.2): the 837P doesn't need them.</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Confirm, or name which contact fields billing staff need and why.</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-047); R-5.1.2</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>Before PI2 merge</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>OA-048</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Decide what happens to synced patients when a practice disconnects or switches EHRs: stay read-only, convert back to manual, or link to the new connection.</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Offboarding and EHR migrations need a defined path; nothing is ever deleted (R-9.2.1).</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Chosen rule.</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-048); R-9.2.1</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>OA-049</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Vendor/Account</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Register DenialDesk as a backend-services app in vendor FHIR sandboxes (Epic on FHIR, Oracle Health, athenahealth) and decide whether to allow-list them in pre-production.</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Pre-production uses only the built-in synthetic sandbox today; vendor sandboxes (synthetic data) test real EHR behavior.</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Which vendors, the sandbox accounts set up by the owner (no secrets in this sheet), and a yes/no on allow-listing them in pre-production.</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-049); ADR 0003</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>Before PI4</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>OA-050</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Approve building FHIR Bulk Data export (PI4) before the first real practice is connected.</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>US Core does not require the population-wide search PI2 uses; certified EHRs offer Bulk Data for population access.</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no and target date.</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-050)</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>OA-051</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Decide who confirms at onboarding that the practice's EHR app registration only exposes that practice's own patients.</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Minimum necessary (R-5.1.2): a registration scoped to a whole health system would over-collect.</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Named role (practice admin, DenialDesk onboarding, or both) and the onboarding checklist step.</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-051); R-5.1.2</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>OA-052</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Decide how to handle patients the EHR labels restricted or very restricted (R/V) until sensitivity masking (patients P4) ships: import them showing 'Restricted in source', or hold them back from sync.</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Threat model I3 is blocking before real data.</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>Chosen rule.</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-052); R-3.5.1</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>OA-053</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether MRN conflicts (same MRN, different birth date) are fixed in the EHR only, or need an admin tool in DenialDesk.</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Conflicts are reported and skipped; a practice needs a way to clear them.</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Chosen approach.</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-053)</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>Before PI3</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>OA-054</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Assign a requirement ID for EHR/PM interoperability (REQUIREMENTS §8.8 has no numbered item for it).</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Every change must map to a requirement ID (CLAUDE.md).</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Approve a new ID (e.g. R-8.8.1) and its wording.</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-054); REQUIREMENTS §8.8</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>Before PI1 merge</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>OA-055</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Confirm that dependents (policy subscriber is not the patient) get no synced coverage until patients P2 adds subscriber details.</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Their claims can't be billed from synced data until then.</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Accept, or reprioritize patients P2.</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-055)</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>Before PI2 merge</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr"/>
+      <c r="L55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>OA-056</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Confirm a 15-minute scheduled patient sync interval.</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Balances freshness against EHR API rate limits.</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Interval (or 'on demand only').</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-056)</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-27</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>Before PI3</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr"/>
+      <c r="L56" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L43"/>
+  <autoFilter ref="A1:L56"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$57</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3488,8 +3488,62 @@
       <c r="K56" s="3" t="inlineStr"/>
       <c r="L56" s="3" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>OA-057</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Confirm the safeguard against one practice pulling another practice's EHR patients: the platform operator approves every real EHR connection after checking its address and client ID with the practice's EHR administrator, the same EHR registration can't be used by two practices, and each connection gets its own signing key where the EHR vendor supports it.</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Security review 2026-09-28 (Critical C1): with one shared DenialDesk signing key, a practice admin could enter another practice's EHR address and client ID and sync its patients.</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Accept the three safeguards, or choose differently (e.g. per-practice keys only).</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (OA-057); R-7.2.4</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>Before PI1b</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L56"/>
+  <autoFilter ref="A1:L57"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$45</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2840,8 +2840,62 @@
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>OA-045</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Confirm three settings for payer custom fields: (1) who may edit a payer's custom field values -- today admin+manager (canEditPayerFields), narrower than the claim/patient roles which also include specialists; (2) that a specialist may still open ('reveal') a locked payer value they cannot edit, since reveal uses the same single reveal-role rule as every other record type (canWorkDenials, ADR 0007) rather than canEditPayerFields; (3) whether payer custom field values are Confidential business data or PHI, since free text on a payer field could still hold patient details, and whether the six patient-oriented sensitivity categories (HIV, mental health, SUD, genetic, minor, reproductive health) are the right lock for a payer field at all, or whether a generic 'confidential' category should be added.</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Payers are practice configuration, not a patient record, but their custom fields are free text an administrator could still use to record something patient-specific; the current role split and sensitivity categories are the implementing agent's best guess (R-5.1.2 minimum necessary), not an owner decision.</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>A yes/confirm on the current role split (or a different role list), confirmation of the data classification, and a decision on whether to add a payer-appropriate sensitivity category.</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>specs/settings-and-custom-fields.md; R-5.1.2</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>custom-fields PR 4 session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>Before first real practice</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L43"/>
+  <autoFilter ref="A1:L45"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$60</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3650,8 +3650,62 @@
       <c r="K59" s="3" t="inlineStr"/>
       <c r="L59" s="3" t="inlineStr"/>
     </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>OA-060</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Confirm that patient names read only to order the unsubmitted claims queue by patient (never shown or returned beyond the displayed page) are covered by the claim.list_viewed audit event and need no separate audit event.</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Settles whether sort-only PHI reads need their own audit trail (R-7.5.1) or only minimum-necessary handling (R-5.1.2).</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Yes (covered) / No (add an audit event for sort-only reads).</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>R-7.5.1, R-5.1.2; specs/record-pages.md P4</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>compliance-checker 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr"/>
+      <c r="L60" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L59"/>
+  <autoFilter ref="A1:L60"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$61</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3704,8 +3704,62 @@
       <c r="K60" s="3" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>OA-061</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Confirm four PI1b step-up/attestation choices made in code review (PR #81), cross-referencing OA-045 and OA-057: (a) step-up window is 5 minutes, a fresh sign-in TOTP counts as step-up, the session token/cookie rotates on successful step-up, and the shared sign-in lockout counter applies to step-up attempts but a successful step-up does NOT reset it; (b) TOTP is accepted as the step-up factor for now — this is a known gap against R-7.2.2's phishing-resistant MFA (WebAuthn) and should be closed before the first real (non-sandbox) EHR connection goes live; (c) the U.S.-residency attestation was moved from Submit (not yet built) to connection create/edit, and is re-confirmed (or re-attested) whenever the endpoint changes or the box is unchecked, rather than being a one-time record; (d) suggested attestation wording for counsel to review: "This EHR/PM endpoint, operated on behalf of {practice name}, stores and processes DenialDesk patient data only in the United States," and which language version (English/Spanish/Portuguese) is the binding one if a practice attests in a non-English locale.</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Security/compliance review of PI1b (PR #81) surfaced these as owner-confirmable defaults rather than agent judgment calls; (b) is a recorded gap against a named requirement, (c) changes when/how a legal attestation is captured, and (d) is text a customer will click through, all of which need a human decision, not an agent's best guess.</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Confirm (a)-(c) as built, or say what to change; confirm or edit the (d) wording and confirm which language is binding.</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md; R-7.2.2, R-3.3.1; cross-ref OA-045, OA-057</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations PI1b review-fix session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Before first real (non-sandbox) EHR connection</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L60"/>
+  <autoFilter ref="A1:L61"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -3025,7 +3025,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Decide what happens to synced patients when a practice disconnects or switches EHRs: stay read-only, convert back to manual, or link to the new connection.</t>
+          <t>Decide what happens to synced patients when a practice disconnects or switches EHRs: stay read-only, convert back to manual, or link to the new connection. Also: after a connection is revoked, synced patients stay read-only and no longer update — how is an amendment request honored for them (45 CFR 164.504(e)(2)(ii)(F); counsel)?</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$61</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3704,8 +3704,62 @@
       <c r="K60" s="3" t="inlineStr"/>
       <c r="L60" s="3" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>OA-061</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Confirm you accept that the free-text EHR/PM connection name is shown to every role on every signed-in page (the Patients data-source drop-down), guarded only by a 'no patient information' hint and length/invisible-character checks — or ask for a stronger guard (e.g. refuse names that look like MRNs or person names).</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>The name now appears in the header of every page, including screen shares and screenshots; only the owner can accept the residual risk.</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Accept as is / require a stronger guard (which).</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>R-7.4.8, R-5.1.2; specs/patient-integrations.md PI1b; specs/erp-shell.md</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>compliance-checker 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>Before first real practice</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr"/>
+      <c r="L61" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L60"/>
+  <autoFilter ref="A1:L61"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$62</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3758,8 +3758,62 @@
       <c r="K61" s="3" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>OA-062</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether the FHIR transport should require TLS 1.3 as a minimum.</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>R-7.3.1 requires TLS 1.2+ and prefers 1.3. The transport allows 1.2 (ECDHE + AEAD suites only) and negotiates 1.3 when offered. Requiring 1.3 is stronger but would lock out EHR vendors that only support 1.2.</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Keep TLS 1.2 minimum (current), or require 1.3 (and, if so, which vendors are known to be 1.2-only).</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md PI2a; R-7.3.1</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>agent 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L61"/>
+  <autoFilter ref="A1:L62"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$62</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3758,8 +3758,62 @@
       <c r="K61" s="3" t="inlineStr"/>
       <c r="L61" s="3" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>OA-063</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Confirm the step-up MFA choices built in PI2a (cross-ref OA-045): (a) the step-up window is 5 minutes, and a fresh sign-in TOTP counts as a step-up; (b) a successful step-up rotates the session token and cookie; (c) step-up attempts share the sign-in lockout counter, a failed one never resets it, and a successful one keeps earlier failures and gives back only its own attempt (so successful step-ups can't add up to a lockout); (d) step-up is required to Resume a paused or errored connection (and, once built, Submit and payer mapping) but NOT to Pause or Revoke, because those are the safe direction and the emergency stop for a suspected compromise; (e) TOTP is the only step-up factor for now: a known gap against R-7.2.2's phishing-resistant MFA (WebAuthn), to close before the first real (non-sandbox) EHR connection goes live.</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Step-up is the control that stops a hijacked or unattended admin session from restarting patient sync; these are owner-confirmable defaults rather than agent judgment calls, and (e) is a recorded gap against a named requirement that needs a human decision on timing.</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Confirm (a)-(d) as built or say what to change; decide whether WebAuthn (or another phishing-resistant factor) must ship before the first real EHR connection, or whether TOTP is accepted until then.</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md PI2a; R-7.2.2; cross-ref OA-045</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>patient-integrations PI2a lifecycle session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>Before first real (non-sandbox) EHR connection</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+      <c r="L62" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L61"/>
+  <autoFilter ref="A1:L62"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$63</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3812,8 +3812,62 @@
       <c r="K62" s="3" t="inlineStr"/>
       <c r="L62" s="3" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>OA-063</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Vendor/Account</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Generate a pre-production ES384 signing key and set it as INTEGRATION_SIGNING_KEY, a functions-only secret, in the Netlify site settings.</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Test connection and the token request sign with this shared key, and its public half is published at /.well-known/jwks.json for a vendor sandbox administrator to register. Without it, Test connection reports that the signing key isn't configured. Never use it in production (production refuses it) and never commit it.</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Confirmation that the secret is set for the Netlify functions only (not the build or the client), and the JWKS URL once it serves a key. Generate with: openssl ecparam -name secp384r1 -genkey -noout | openssl pkcs8 -topk8 -nocrypt (PKCS#8 PEM).</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md PI2a Keys; R-7.3.4, R-7.3.5</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>agent 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>Before testing against a vendor sandbox</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L62"/>
+  <autoFilter ref="A1:L63"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -3781,7 +3781,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Confirm the step-up MFA choices built in PI2a (cross-ref OA-045): (a) the step-up window is 5 minutes, and a fresh sign-in TOTP counts as a step-up; (b) a successful step-up rotates the session token and cookie; (c) step-up attempts share the sign-in lockout counter, a failed one never resets it, and a successful one keeps earlier failures and gives back only its own attempt (so successful step-ups can't add up to a lockout); (d) step-up is required to Resume a paused or errored connection (and, once built, Submit and payer mapping) but NOT to Pause or Revoke, because those are the safe direction and the emergency stop for a suspected compromise; (e) TOTP is the only step-up factor for now: a known gap against R-7.2.2's phishing-resistant MFA (WebAuthn), to close before the first real (non-sandbox) EHR connection goes live.</t>
+          <t>Confirm the step-up MFA choices built in PI2a (cross-ref OA-045): (a) the step-up window is 5 minutes, and a fresh sign-in TOTP counts as a step-up; (b) a successful step-up rotates the session token and cookie; (c) step-up attempts share the sign-in lockout counter, a failed one never resets it, and a successful one keeps earlier failures and gives back only its own attempt (so successful step-ups can't add up to a lockout), and the attempt that would reach the lockout limit is refused before its code is checked (so a correct code can never lock the account); (d) step-up is required to Resume a paused or errored connection (and, once built, Submit and payer mapping) but NOT to Pause or Revoke, because those are the safe direction and the emergency stop for a suspected compromise; (e) TOTP is the only step-up factor for now: a known gap against R-7.2.2's phishing-resistant MFA (WebAuthn), to close before the first real (non-sandbox) EHR connection goes live.</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -3781,7 +3781,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>Confirm the step-up MFA choices built in PI2a (cross-ref OA-045): (a) the step-up window is 5 minutes, and a fresh sign-in TOTP counts as a step-up; (b) a successful step-up rotates the session token and cookie; (c) step-up attempts share the sign-in lockout counter, a failed one never resets it, and a successful one keeps earlier failures and gives back only its own attempt (so successful step-ups can't add up to a lockout), and the attempt that would reach the lockout limit is refused before its code is checked (so a correct code can never lock the account); (d) step-up is required to Resume a paused or errored connection (and, once built, Submit and payer mapping) but NOT to Pause or Revoke, because those are the safe direction and the emergency stop for a suspected compromise; (e) TOTP is the only step-up factor for now: a known gap against R-7.2.2's phishing-resistant MFA (WebAuthn), to close before the first real (non-sandbox) EHR connection goes live.</t>
+          <t>Confirm the step-up MFA choices built in PI2a (cross-ref OA-045): (a) the step-up window is 5 minutes, and a fresh sign-in TOTP counts as a step-up; (b) a successful step-up rotates the session token and cookie; (c) step-up attempts share the sign-in lockout counter, a failed one never resets it, and a successful one keeps earlier failures and gives back only its own attempt (so successful step-ups can't add up to a lockout), and the attempt that would reach the lockout limit is refused before its code is checked and is what locks the account for the usual 15 minutes, audited as auth.locked_out (so a correct code never causes the lock, and the lock expires on its own; an attempt while already locked is audited as auth.step_up_refused); (d) step-up is required to Resume a paused or errored connection (and, once built, Submit and payer mapping) but NOT to Pause or Revoke, because those are the safe direction and the emergency stop for a suspected compromise; (e) TOTP is the only step-up factor for now: a known gap against R-7.2.2's phishing-resistant MFA (WebAuthn), to close before the first real (non-sandbox) EHR connection goes live.</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$65</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3920,8 +3920,62 @@
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>OA-065</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Confirm two PI2a coordinator decisions: (a) Submit's Test-connection gate is stricter than the spec's plain wording — the newest test for the connection must be a pass within 24 h, bound to the tested base URL, client ID, token endpoint and key, issuer, and signing kid (a later failed test or transport refusal voids it); (b) pre-production signs every connection with one shared key (INTEGRATION_SIGNING_KEY), accepted as a pre-production exception with the operator verifying client_id ownership outside the app at approval.</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>(a) decides when a practice may submit a connection; (b) is a residual risk recorded in the threat model (S3): an admin who knows another practice's client_id at the same EHR could get a passing test for it. Synthetic data only; per-connection Key Vault keys remove it in production.</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Confirm (a) and (b) as built, or say what to change (e.g. 'any pass in 24 h counts').</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI2a Test connection, Keys; PI1c Approve); docs/threat-models/patient-integrations.md S3; R-7.3.4, R-7.3.5</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Coordinator (PR #87 compliance review), 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Before Submit ships (next PI2a PR)</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L62"/>
+  <autoFilter ref="A1:L65"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -2647,7 +2647,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Native-speaker review of the Spanish and Portuguese billing terminology (glossary in specs/internationalization.md), plus counsel/compliance sign-off that translated attestations and caveats (synthetic-data attestation, BAA recording labels, uncontestable-obligation alert, R-8.7 suppression and residual-risk text) mean the same thing in law.</t>
+          <t>Native-speaker review of the Spanish and Portuguese billing terminology (glossary in specs/internationalization.md), plus counsel/compliance sign-off that translated attestations and caveats (synthetic-data attestation, BAA recording labels, uncontestable-obligation alert, R-8.7 suppression and residual-risk text) mean the same thing in law. Added with Submit (PR #88): the Spanish and Portuguese U.S.-residency attestation an administrator ticks before submitting a real EHR connection (`submit.attestation`, `submit.attestationHint`, `error.attestationRequired` in src/i18n/messages/es|pt/integrations.ts) are agent-written and need native-speaker review and counsel sign-off that they mean the same as the English text ("This EHR/PM endpoint stores and processes data only in the United States"). The audit event records the displayed language, the wording version, and a SHA-256 of the exact text shown, so a changed translation needs a version bump.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Confirmed or corrected glossary rows; any screen wording to change; counsel sign-off on the listed copy.</t>
+          <t>Confirmed or corrected glossary rows; any screen wording to change; counsel sign-off on the listed copy. For the attestation keys: confirmed or corrected es/pt wording and counsel sign-off (a change means bumping US_RESIDENCY_ATTESTATION_VERSION).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Before the Azure (production) launch</t>
+          <t>Before the first real connection</t>
         </is>
       </c>
       <c r="K41" s="3" t="n"/>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Decide with counsel whether an administrator's U.S.-hosting attestation for the practice's EHR endpoint is enough, or whether DenialDesk must get written confirmation from the EHR vendor; confirm the customer BAA covers DenialDesk pulling patient data from the practice's EHR.</t>
+          <t>Decide with counsel whether an administrator's U.S.-hosting attestation for the practice's EHR endpoint is enough, or whether DenialDesk must get written confirmation from the EHR vendor; confirm the customer BAA covers DenialDesk pulling patient data from the practice's EHR. Also decide, from the PI2a Submit compliance review: (N3) whether a later migration should add a time floor to the Submit stamps (`submitted_at` and `us_residency_attested_at` must be at least `transaction_timestamp()`, so an app-role writer can't back-date or forward-date them) and, optionally, require `us_residency_attested_by = submitted_by` (attested_by being non-null is already enforced by the 0039 CHECKs); due before the first real connection or the Azure cutover, whichever is first. (N6) Whether the attestation should also name backups and disaster-recovery copies and say the endpoint is "accessed only from the United States"; any change to the wording is a new attestation version (US_RESIDENCY_ATTESTATION_VERSION) and needs new es/pt text (OA-041).</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Counsel answer: attestation vs. vendor letter, and BAA wording if a change is needed.</t>
+          <t>Counsel answer: attestation vs. vendor letter, and BAA wording if a change is needed. N3: yes/no on the stamp time floor and on attested_by = submitted_by. N6: the final wording, or confirmation that the current wording stands.</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>Before first real connection</t>
+          <t>Before first real connection (N3: also before the Azure cutover)</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr"/>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Confirm two PI2a coordinator decisions: (a) Submit's Test-connection gate is stricter than the spec's plain wording — the newest test for the connection must be a pass within 24 h, bound to the tested base URL, client ID, token endpoint and key, issuer, and signing kid (a later failed test or transport refusal voids it); (b) pre-production signs every connection with one shared key (INTEGRATION_SIGNING_KEY), accepted as a pre-production exception with the operator verifying client_id ownership outside the app at approval.</t>
+          <t>Confirm three PI2a coordinator decisions: (a) Submit's Test-connection gate is stricter than the spec's plain wording — the newest test for the connection must be a pass within 24 h, bound to the tested base URL, client ID, token endpoint and key, issuer, and signing kid (a later failed test or transport refusal voids it); (b) pre-production signs every connection with one shared key (INTEGRATION_SIGNING_KEY), accepted as a pre-production exception with the operator verifying client_id ownership outside the app at approval. (c) A refused Submit says "This endpoint and client ID are already connected": it reveals that some practice holds that endpoint and client ID pair, with no identity disclosed. It is bounded by the Test connection limits (5 per connection and 20 per practice per 10 minutes) and the Submit limit (10 per practice per 10 minutes), and audited. Accept this signal, or reject it and refuse with the generic 'could not be submitted' wording.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Confirm (a) and (b) as built, or say what to change (e.g. 'any pass in 24 h counts').</t>
+          <t>Confirm (a) and (b) as built, or say what to change (e.g. 'any pass in 24 h counts'). (c) Accept or reject the registry-conflict signal.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Before Submit ships (next PI2a PR)</t>
+          <t>Before the first real connection</t>
         </is>
       </c>
       <c r="K65" s="2" t="n"/>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$73</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3974,8 +3974,440 @@
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>OA-066</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Approve the lists behind Approve's verification record. Verification method: phone call-back to a number on file, video call with the EHR/PM administrator, written confirmation from the administrator's verified address, confirmed in the EHR/PM vendor's app registry. Contact's role at the practice: EHR/PM administrator, practice administrator, practice IT contact, vendor representative, other.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>The spec asks for a "method code" and "the contact's role" but lists neither; the builder proposed these. They are the evidence that the operator verified the connection with the practice out of band, so they should match what onboarding will really do. (OA-051 is a different question: who confirms the population scope.)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the lists, or give the changes (add, remove, rename).</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI1c); src/domain/integrations/approval-codes.ts</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>OA-067</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>R-15.9 sign-off for the operator alert on integration.registry_conflict: allow either (1) a SECURITY DEFINER function integration_registry_conflict_record(connection_id) that Submit calls to write an operator-only record of the HOLDING connection's ID, or (2) an INSERT-only grant on a new operator-only table to the app role.</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>A refused Submit reveals only that some practice holds the endpoint and client ID pair. The operator needs to know who holds it to follow up a squatting or confused-deputy attempt (threat model S2), but the practice's own audit event can't show it, and the record must live outside the tenant's audit log and never reach the customer audit viewer. Writing it from a practice session is a privilege change, so it needs your sign-off; no migration is written until you decide.</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Choose (1) or (2), or reject the alert and say what the operator should rely on instead.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>docs/threat-models/patient-integrations.md S2; docs/specs/patient-integrations.md (PI1c); R-15.9</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="n"/>
+      <c r="L67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>OA-068</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Confirm that Reject should clear the practice's U.S.-residency attestation and the discovered token endpoint/issuer, as Withdraw does (built that way), rather than leave them on the returned draft.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>The spec says only that Reject returns the connection to draft and releases the registry claim. The endpoint becomes editable again, so a different endpoint must be attested and discovered afresh; migration 0042 refuses a stale attestation on the next Submit either way.</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Confirm as built, or say to leave them.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI1c); docs/specs/patient-integrations.md (Withdraw)</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>OA-069</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Write the Notifications spec that the activation notice depends on: who is notified when a connection is approved (all practice administrators), the notice wording, how long notices are kept, and whether a PHI-free e-mail may be sent.</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>The spec requires every practice administrator to be notified on activation (and, wanted, on revoke, SOC 2 CC7.3). The app has no in-app notice mechanism, so nothing is sent today; the practice only sees the new status on its pages. Building a notices system is its own feature.</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Who is notified, retention, and yes/no on PHI-free e-mail; then a builder slice can build the notice.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI1c); specs/settings-and-custom-fields.md S3</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>OA-070</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Decide how long approval evidence is kept: operator.integration_approved and operator.integration_rejected audit events kept for the life of the connection plus 6 years and under legal hold, or add dedicated approval columns (date verified, contact role, ownership confirmed) later.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>The date, the contact's role, and the client-ID ownership confirmation are recorded only in the audit event; the connection row has no columns for them. They are the proof that a real connection was verified with the practice before PHI flowed (HIPAA documentation retention, 45 CFR 164.316(b)(2), six years).</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Retention rule (with counsel if needed), and whether to add columns.</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI1c); R-7.5.1; 45 CFR 164.316(b)(2)</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>OA-071</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Build an operator-side revoke of a live connection before the first real connection, and say who may use it.</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>The lifecycle allows revoke by "admin or operator", but only a practice administrator can revoke today. In a suspected compromise, or when the practice's administrator is unreachable, the platform operator has no way to stop a live sync.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no and the conditions; then a spec item (added, unticked) is built.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI1c); docs/runbooks/integration-offboarding.md</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Before first real connection</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>OA-072</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Accept that operator approval is a single-person control, and confirm that exactly one named person uses the platform operator account. Otherwise plan per-person operator accounts before production.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Approve depends on one account's judgment and one person's out-of-band verification. HIPAA unique user identification (45 CFR 164.312(a)(2)(i)) needs each action attributable to one person; a shared operator account would not be. The audit event records the account and its session, not a person.</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Accept single-person approval (yes/no), and confirm who holds the account; or a plan for per-person operator accounts and a second approver.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI1c); docs/specs/operator-login.md; 45 CFR 164.312(a)(2)(i)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Before production</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>OA-073</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Decide whether Approve must be gated by an operator-realm step-up (fresh second-factor check within a short window), and by when. Reject would stay ungated.</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Practice-side Submit and Resume need a step-up within 5 minutes; the operator's Approve, the control that lets a real connection go live, has none beyond the sign-in session (security review M1). It is not built; recorded as an unticked spec item.</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no and the deadline (proposed: before the Azure cutover and the first real connection); the audit will then record step_up_verified_at.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI1c); R-7.2.2; cross-ref OA-063</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Before Azure cutover</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L65"/>
+  <autoFilter ref="A1:L73"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$66</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3974,8 +3974,62 @@
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
     </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>OA-066</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Review and approve docs/HIPAA_COMPLIANCE.md and docs/SECURE_CODING.md as binding policy, and name the Security Officer and Privacy Officer who sign exceptions to them.</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Both standards are enforced by the reviewer agents now; exceptions have no valid signer until the officers are named (R-10.1), so any conflict blocks the PR.</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>Approval (or requested changes) and the two officers' names.</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>docs/HIPAA_COMPLIANCE.md; docs/SECURE_CODING.md; R-5.2, R-7.4.1, R-10.1, R-15.7</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>agent session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L65"/>
+  <autoFilter ref="A1:L66"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -4007,7 +4007,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>Approval (or requested changes) and the two officers' names.</t>
+          <t>Approval (or requested changes); the two officers' names; confirmation that branch protection on main requires pull requests and CI and blocks force pushes (SC-B12.4); and counsel confirmation of HC-9.3 (FIPA 10-day third-party-agent notice to the practice, HIPAA BA clock), HC-1.4 (any use of de-identified data outside a tenant), and the Florida sensitive-category statutes in HC-1.5.</t>
         </is>
       </c>
       <c r="H66" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$76</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4406,8 +4406,170 @@
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
     </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>OA-074</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Approve ADR 0011 (field-encryption v2 envelope with key ID and mandatory AAD; 'global' scope for TOTP secrets, operator included) and answer spec questions 2-5: run the re-encryption job on pre-production or wipe and re-seed; who confirms the legacy cut-off and when; confirm Azure production starts empty; say whether the pre-production FIELD_ENCRYPTION_KEY was ever changed.</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Member IDs and TOTP secrets are encrypted without AAD (SECURE_CODING known gap SC-B7.1); the build (PRs 1-5) waits on this approval.</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Approval or requested changes to ADR 0011; answers to questions 2-5 in docs/specs/field-encryption-aad.md.</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1; R-7.3.3; ADR 0011; docs/specs/field-encryption-aad.md</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Before the SC-B7.1 build</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr"/>
+      <c r="L74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>OA-075</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Approve a separate RATE_LIMIT_HASH_KEY so src/lib/rate-limit.ts stops reusing FIELD_ENCRYPTION_KEY as a hash salt (spec question 6).</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>One key per purpose; rotating the field key must not reset rate-limit windows.</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no; if yes the agent adds the variable in a follow-up PR (never the value in the sheet).</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1; R-7.3.4; docs/specs/field-encryption-aad.md</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Before the first key rotation</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>OA-076</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Decide the ADR 0011 follow-ups (spec questions 7-9): keep retired keys decrypt-only for append-only custom-field history and synced patients or approve a re-encryption path (R-15.9); run one pre-production key-rotation drill after the cut-off; whether an 835 or find-by-member-ID feature gets a tenant-keyed blind index.</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Shapes the Azure-cutover key rotation ADR and any member-ID matching feature.</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>An answer to each of the three; the rotation part can wait for the cutover ADR.</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1; R-7.3.4; R-15.9; docs/specs/field-encryption-aad.md</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>Azure cutover</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L73"/>
+  <autoFilter ref="A1:L76"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -4439,7 +4439,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Approval (or requested changes); the two officers' names; confirmation that branch protection on the default branch (see OA-001) requires pull requests and CI and blocks force pushes (SC-B12.4); and counsel confirmation of HC-9.3 (FIPA 10-day third-party-agent notice to the practice, HIPAA BA clock), HC-1.4 (any use of de-identified data outside a tenant), and the Florida sensitive-category statutes in HC-1.5.</t>
+          <t>Approval (or requested changes); the two officers' names; confirmation that branch protection on the default branch (see OA-001) requires pull requests and CI and blocks force pushes (SC-B12.4); and counsel confirmation of HC-9.3 (FIPA 10-day third-party-agent notice to the practice, HIPAA BA clock), HC-1.4 (any use of de-identified data outside a tenant), and the Florida sensitive-category statutes in HC-1.5; and a yes/no on adding `@rolldown/binding-*` and `fsevents` (dev-tool native binaries already in the lockfile) to the SC-A2.5 exception list.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>docs/HIPAA_COMPLIANCE.md; docs/SECURE_CODING.md; R-5.2, R-7.4.1, R-10.1, R-15.7</t>
+          <t>docs/HIPAA_COMPLIANCE.md; docs/SECURE_CODING.md; R-7.4.1, R-7.4.2, R-10.1, R-15.7</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -4409,7 +4409,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>OA-074</t>
+          <t>OA-077</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$75</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4406,8 +4406,116 @@
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>OA-074</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Decide whether CI (and local development) runs the integration suite as a non-superuser, NOBYPASSRLS schema-owner role, so FORCE ROW LEVEL SECURITY is exercised on the owner and platform paths.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>CI connects to PostgreSQL as a superuser, which ignores row-level security even on FORCE tables, so tests never exercise the owner path (`withTenantAsPlatform`: operator Approve and Reject, BAAs, University access) or owner-role reads under the tenant policy. A missing `app.tenant_id` or a policy that hides rows from the owner would pass CI and surface at the first non-superuser deploy (Netlify preview, Azure). Changing the CI database role is a privilege change, so it needs the owner's sign-off (R-15.9).</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no and the timing. Proposal: migrate and run `pnpm test:integration` as a non-superuser, NOBYPASSRLS owner role (setup that must bypass policies keeps a separate superuser connection), plus a test that the connection role has neither rolsuper nor rolbypassrls. Then a CI and docker-compose change is built.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (Test infrastructure gap); docs/PROJECT_STATE.md; R-15.9; R-7.2.4</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>PI2b UI slice, after PR #89 and PR #91 reviews, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Before the Azure cutover</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>OA-075</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Say whether a payor key (`Organization/&lt;id&gt;`, an insurer reference reported by the EHR/PM) is detached from any patient's PHI, or is PHI where it sits on a patient row.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>The key names an insurer, not a person, but it is stored on each synced patient row (`coverage_payor_key`, classified Restricted PHI) and repeated in `integration_payer_mappings` (classified Confidential configuration). The answer decides whether the mapping table is reclassified from Confidential to Restricted (access, audit, retention, and log handling follow the class). Until answered, the payer mapping page is audited and no audit event or log carries a key.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Detached (keep Confidential) or not detached (reclassify to Restricted), with the reasoning counsel or the compliance owner accepts.</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (Classification, PI2b); REQUIREMENTS §9.1</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>PI2b UI slice, compliance review of PR #91, 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Before the first real connection</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L73"/>
+  <autoFilter ref="A1:L75"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$77</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>Decide the ADR 0011 follow-ups (spec questions 7-9): keep retired keys decrypt-only for append-only custom-field history and synced patients or approve a re-encryption path (R-15.9); run one pre-production key-rotation drill after the cut-off; whether an 835 or find-by-member-ID feature gets a tenant-keyed blind index.</t>
+          <t>Decide the ADR 0011 follow-ups (spec questions 7-10): keep retired keys decrypt-only for append-only custom-field history and synced patients or approve a re-encryption path (R-15.9); key retirement: backup and point-in-time retention periods, no key destruction until legal hold exists, and Security plus Privacy Officer sign-off to destroy a key; run one pre-production key-rotation drill after the cut-off; whether an 835 or find-by-member-ID feature gets a tenant-keyed blind index.</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -4568,8 +4568,62 @@
       <c r="K76" s="3" t="inlineStr"/>
       <c r="L76" s="3" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>OA-078</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether rcm_claim_lines.account_number (the practice's patient account number in revenue-cycle files) is field-encrypted like member IDs.</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>HC-7.3/R-7.3.3 list only SSN, MBI, member IDs, and bank data, so plaintext breaks no MUST rule today; it is still an HC-1.1 identifier protected only by at-rest encryption and RLS.</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no from the Security and Privacy Officers; if yes, the agent adds it to the ADR 0011 build.</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1; HC-1.1; HC-7.3; ADR 0011; docs/specs/field-encryption-aad.md</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1 AAD plan session 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L76"/>
+  <autoFilter ref="A1:L77"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$75</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L74"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4460,8 +4460,62 @@
       <c r="K74" s="2" t="n"/>
       <c r="L74" s="2" t="n"/>
     </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>OA-079</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether local development may keep Next.js's unavoidable 'next dev' update check (it asks registry.npmjs.org for newer Next.js versions; no opt-out in 16.3.6) under a written, time-boxed exception ADR signed by the Security and Privacy Officers (HC §0), or keep SC-A2.6 tracked as a known gap.</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>SC-A2.6 bans update checks; everything else that phones home is now off. No PHI is involved (local development holds synthetic data only).</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Accept (officers sign an exception ADR the agent drafts) or keep tracked.</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>SC-A2.6; HC §0; PR #96</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>SC gap PRs session 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L73"/>
+  <autoFilter ref="A1:L75"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -4547,7 +4547,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>An answer to each of the three; the rotation part can wait for the cutover ADR.</t>
+          <t>An answer to each of the four (rotation path, key retirement policy, drill, blind index); the rotation parts can wait for the cutover ADR.</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -4561,7 +4561,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>APPROVED by the owner 2026-09-29 (R-15.9): the integration service-principal seed in migration 0043 (disabled `users` row, unusable password hash, no membership, no session, no second factor). No GRANT, REVOKE, role, SECURITY DEFINER or RLS change. Follow-up, not a change to 0043: a later migration should use ON CONFLICT (id) DO NOTHING (PR #98 review L3).</t>
+          <t>APPROVED by the owner 2026-09-29 (R-15.9): the integration service-principal seed in migration 0043 (disabled `users` row, unusable password hash, no membership, no session, no second factor). No GRANT, REVOKE, role, SECURITY DEFINER or RLS change. Follow-up, not a change to 0043: a later migration should use ON CONFLICT (id) DO NOTHING (PR #98 review L3). Approval evidence: https://github.com/jselvalugo/DenialDesk/pull/98#issuecomment-5881787399</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$82</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -59,15 +59,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -435,16 +432,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="7"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -2621,8 +2615,8 @@
           <t>Before general availability</t>
         </is>
       </c>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2675,8 +2669,8 @@
           <t>Before the first real connection</t>
         </is>
       </c>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2729,62 +2723,62 @@
           <t>Owner decision; not blocking</t>
         </is>
       </c>
-      <c r="K42" s="3" t="n"/>
-      <c r="L42" s="3" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>OA-043</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Confirm the patient list may show sex and city/state beside name, MRN and date of birth (minimum necessary), and whether restricted (sensitivity-tagged) rows should keep hiding them.</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Compliance-checker flagged the new list columns (record pattern P1) as a minimum-necessary question; the list hides them for tagged rows until decided.</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Keep / drop each column; keep or lift the restricted-row rule.</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>specs/record-pages.md; 45 CFR 164.502(b)</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>record-pages session 2026-09-27</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2841,922 +2835,922 @@
       <c r="L44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>OA-045</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Decide with counsel whether an administrator's U.S.-hosting attestation for the practice's EHR endpoint is enough, or whether DenialDesk must get written confirmation from the EHR vendor; confirm the customer BAA covers DenialDesk pulling patient data from the practice's EHR. Also decide, from the PI2a Submit compliance review: (N3) whether a later migration should add a time floor to the Submit stamps (`submitted_at` and `us_residency_attested_at` must be at least `transaction_timestamp()`, so an app-role writer can't back-date or forward-date them) and, optionally, require `us_residency_attested_by = submitted_by` (attested_by being non-null is already enforced by the 0039 CHECKs); due before the first real connection or the Azure cutover, whichever is first. (N6) Whether the attestation should also name backups and disaster-recovery copies and say the endpoint is "accessed only from the United States"; any change to the wording is a new attestation version (US_RESIDENCY_ATTESTATION_VERSION) and needs new es/pt text (OA-041).</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Fla. Stat. § 408.051(3) data residency and the BAA scope gate every real EHR connection.</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Counsel answer: attestation vs. vendor letter, and BAA wording if a change is needed. N3: yes/no on the stamp time floor and on attested_by = submitted_by. N6: the final wording, or confirmation that the current wording stands.</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-045); R-3.3.1</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>Before first real connection (N3: also before the Azure cutover)</t>
         </is>
       </c>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>OA-046</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Decide whether to retire manual patient registration once a practice's EHR is connected, and what happens to older manually entered patients that never match a synced record.</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>The owner asked that DenialDesk sync patients rather than hold them; manual entry is kept only for practices without a connection.</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Yes/no on retiring manual registration, plus the rule for unmatched manual patients (stay read-only, archive, or editable).</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-046)</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J46" s="3" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Before PI3</t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>OA-047</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Confirm that patient phone and email are not synced from the EHR (billing minimum only).</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Minimum necessary (R-5.1.2): the 837P doesn't need them.</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Confirm, or name which contact fields billing staff need and why.</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-047); R-5.1.2</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>Before PI2 merge</t>
         </is>
       </c>
-      <c r="K47" s="3" t="inlineStr"/>
-      <c r="L47" s="3" t="inlineStr"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>OA-048</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Decide what happens to synced patients when a practice disconnects or switches EHRs: stay read-only, convert back to manual, or link to the new connection. Also: after a connection is revoked, synced patients stay read-only and no longer update — how is an amendment request honored for them (45 CFR 164.504(e)(2)(ii)(F); counsel)?</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Offboarding and EHR migrations need a defined path; nothing is ever deleted (R-9.2.1).</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Chosen rule.</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-048); R-9.2.1</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K48" s="3" t="inlineStr"/>
-      <c r="L48" s="3" t="inlineStr"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>OA-049</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Vendor/Account</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Register DenialDesk as a backend-services app in vendor FHIR sandboxes (Epic on FHIR, Oracle Health, athenahealth) and decide whether to allow-list them in pre-production.</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Pre-production uses only the built-in synthetic sandbox today; vendor sandboxes (synthetic data) test real EHR behavior.</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Which vendors, the sandbox accounts set up by the owner (no secrets in this sheet), and a yes/no on allow-listing them in pre-production.</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-049); ADR 0003</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J49" s="3" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Before PI4</t>
         </is>
       </c>
-      <c r="K49" s="3" t="inlineStr"/>
-      <c r="L49" s="3" t="inlineStr"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>OA-050</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Approve building FHIR Bulk Data export (PI4) before the first real practice is connected.</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>US Core does not require the population-wide search PI2 uses; certified EHRs offer Bulk Data for population access.</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Yes/no and target date.</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-050)</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J50" s="3" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K50" s="3" t="inlineStr"/>
-      <c r="L50" s="3" t="inlineStr"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>OA-051</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Decide who confirms at onboarding that the practice's EHR app registration only exposes that practice's own patients.</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Minimum necessary (R-5.1.2): a registration scoped to a whole health system would over-collect.</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>Named role (practice admin, DenialDesk onboarding, or both) and the onboarding checklist step.</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-051); R-5.1.2</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr"/>
-      <c r="L51" s="3" t="inlineStr"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>OA-052</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Decide how to handle patients the EHR labels restricted or very restricted (R/V) until sensitivity masking (patients P4) ships: import them showing 'Restricted in source', or hold them back from sync.</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Threat model I3 is blocking before real data.</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Chosen rule.</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-052); R-3.5.1</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K52" s="3" t="inlineStr"/>
-      <c r="L52" s="3" t="inlineStr"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>OA-053</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Decide whether MRN conflicts (same MRN, different birth date) are fixed in the EHR only, or need an admin tool in DenialDesk.</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Conflicts are reported and skipped; a practice needs a way to clear them.</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Chosen approach.</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-053)</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>Before PI3</t>
         </is>
       </c>
-      <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>OA-054</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Assign a requirement ID for EHR/PM interoperability (REQUIREMENTS §8.8 has no numbered item for it).</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Every change must map to a requirement ID (CLAUDE.md).</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Approve a new ID (e.g. R-8.8.1) and its wording.</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-054); REQUIREMENTS §8.8</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>Before PI1 merge</t>
         </is>
       </c>
-      <c r="K54" s="3" t="inlineStr"/>
-      <c r="L54" s="3" t="inlineStr"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>OA-055</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Confirm that dependents (policy subscriber is not the patient) get no synced coverage until patients P2 adds subscriber details.</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Their claims can't be billed from synced data until then.</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Accept, or reprioritize patients P2.</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-055)</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>Before PI2 merge</t>
         </is>
       </c>
-      <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>OA-056</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Confirm a 15-minute scheduled patient sync interval.</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Balances freshness against EHR API rate limits.</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Interval (or 'on demand only').</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-056)</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>Before PI3</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr"/>
-      <c r="L56" s="3" t="inlineStr"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>OA-057</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Confirm the safeguard against one practice pulling another practice's EHR patients: the platform operator approves every real EHR connection after checking its address and client ID with the practice's EHR administrator, the same EHR registration can't be used by two practices, and each connection gets its own signing key where the EHR vendor supports it.</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Security review 2026-09-28 (Critical C1): with one shared DenialDesk signing key, a practice admin could enter another practice's EHR address and client ID and sync its patients.</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Accept the three safeguards, or choose differently (e.g. per-practice keys only).</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-057); R-7.2.4</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-28</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Before PI1b</t>
         </is>
       </c>
-      <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>OA-058</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Confirm that practice-wide denial totals without identifiers (counts and sums on the home page) are not a PHI read and need no audit event.</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>The home page revamp shows live open-denial totals without auditing each view; Insight reports audit aggregates as PHI-adjacent, so the rule should be set once.</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Yes/no; if no, the agent adds an audit event to the home page strip.</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>R-7.5.1; specs/welcome-page.md</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>home-page revamp session 2026-09-27</t>
         </is>
       </c>
-      <c r="J58" s="3" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Before the Azure (production) launch</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr"/>
-      <c r="L58" s="3" t="inlineStr"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>OA-059</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Confirm three settings for payer custom fields: (1) who may edit a payer's custom field values -- today admin+manager (canEditPayerFields), narrower than the claim/patient roles which also include specialists; (2) that a specialist may still open ('reveal') a locked payer value they cannot edit, since reveal uses the same single reveal-role rule as every other record type (canWorkDenials, ADR 0007) rather than canEditPayerFields; (3) whether payer custom field values are Confidential business data or PHI, since free text on a payer field could still hold patient details, and whether the six patient-oriented sensitivity categories (HIV, mental health, SUD, genetic, minor, reproductive health) are the right lock for a payer field at all, or whether a generic 'confidential' category should be added.</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Payers are practice configuration, not a patient record, but their custom fields are free text an administrator could still use to record something patient-specific; the current role split and sensitivity categories are the implementing agent's best guess (R-5.1.2 minimum necessary), not an owner decision.</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>A yes/confirm on the current role split (or a different role list), confirmation of the data classification, and a decision on whether to add a payer-appropriate sensitivity category.</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>specs/settings-and-custom-fields.md; R-5.1.2</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>custom-fields PR 4 session 2026-09-28</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Before first real practice</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>OA-060</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Confirm that patient names read only to order the unsubmitted claims queue by patient (never shown or returned beyond the displayed page) are covered by the claim.list_viewed audit event and need no separate audit event.</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Settles whether sort-only PHI reads need their own audit trail (R-7.5.1) or only minimum-necessary handling (R-5.1.2).</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Yes (covered) / No (add an audit event for sort-only reads).</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>R-7.5.1, R-5.1.2; specs/record-pages.md P4</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>compliance-checker 2026-09-28</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr"/>
-      <c r="L60" s="3" t="inlineStr"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>OA-061</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Confirm you accept that the free-text EHR/PM connection name is shown to every role on every signed-in page (the Patients data-source drop-down), guarded only by a 'no patient information' hint and length/invisible-character checks — or ask for a stronger guard (e.g. refuse names that look like MRNs or person names).</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>The name now appears in the header of every page, including screen shares and screenshots; only the owner can accept the residual risk.</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>Accept as is / require a stronger guard (which).</t>
         </is>
       </c>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>R-7.4.8, R-5.1.2; specs/patient-integrations.md PI1b; specs/erp-shell.md</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>compliance-checker 2026-09-28</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>Before first real practice</t>
         </is>
       </c>
-      <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
+      <c r="K61" s="2" t="n"/>
+      <c r="L61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3813,58 +3807,58 @@
       <c r="L62" s="2" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>OA-063</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Confirm the step-up MFA choices built in PI2a (cross-ref OA-045): (a) the step-up window is 5 minutes, and a fresh sign-in TOTP counts as a step-up; (b) a successful step-up rotates the session token and cookie; (c) step-up attempts share the sign-in lockout counter, a failed one never resets it, and a successful one keeps earlier failures and gives back only its own attempt (so successful step-ups can't add up to a lockout), and the attempt that would reach the lockout limit is refused before its code is checked and is what locks the account for the usual 15 minutes, audited as auth.locked_out (so a correct code never causes the lock, and the lock expires on its own; an attempt while already locked is audited as auth.step_up_refused); (d) step-up is required to Resume a paused or errored connection (and, once built, Submit and payer mapping) but NOT to Pause or Revoke, because those are the safe direction and the emergency stop for a suspected compromise; (e) TOTP is the only step-up factor for now: a known gap against R-7.2.2's phishing-resistant MFA (WebAuthn), to close before the first real (non-sandbox) EHR connection goes live.</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Step-up is the control that stops a hijacked or unattended admin session from restarting patient sync; these are owner-confirmable defaults rather than agent judgment calls, and (e) is a recorded gap against a named requirement that needs a human decision on timing.</t>
         </is>
       </c>
-      <c r="G63" s="3" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Confirm (a)-(d) as built or say what to change; decide whether WebAuthn (or another phishing-resistant factor) must ship before the first real EHR connection, or whether TOTP is accepted until then.</t>
         </is>
       </c>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md PI2a; R-7.2.2; cross-ref OA-045</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>patient-integrations PI2a lifecycle session 2026-09-28</t>
         </is>
       </c>
-      <c r="J63" s="3" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>Before first real (non-sandbox) EHR connection</t>
         </is>
       </c>
-      <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4514,14 +4508,409 @@
       <c r="K75" s="2" t="n"/>
       <c r="L75" s="2" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>OA-076</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Sign off (R-15.9) on migration 0043 before it runs anywhere beyond a local or test database: it seeds one identity, the integration service-principal `users` row (id d3a7c0de-5a1c-4e11-8a0c-0000000d0d01, disabled, unusable password hash, no membership, no session, no second factor) that the sync engine writes as. It adds no GRANT, REVOKE, role, SECURITY DEFINER function, or RLS policy change.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>The sync engine's audit events and its `updated_by` on connection and payer-mapping rows need a user row (foreign keys). A seeded account is an identity change under R-15.9 even though it cannot sign in. The same migration also changes two trigger functions (stamp `updated_at` with the real clock on status changes; abandon queued and running runs on pause and error) and replaces the sandbox CHECK constraint (the issuer is the base URL), none of which changes a privilege.</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Approve, or ask for a different shape (for example an account outside `users`, which would mean dropping the foreign keys the engine writes under). Recorded on the PR.</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI2b); drizzle/0043_patient_integrations_sync_engine.sql; R-15.9</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>PI2b sync engine builder, 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Done 2026-09-29 (was: before 0043 runs beyond local and test databases; Netlify previews already applied it)</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>APPROVED by the owner 2026-09-29 (R-15.9): the integration service-principal seed in migration 0043 (disabled `users` row, unusable password hash, no membership, no session, no second factor). No GRANT, REVOKE, role, SECURITY DEFINER or RLS change. Follow-up, not a change to 0043: a later migration should use ON CONFLICT (id) DO NOTHING (PR #98 review L3). Approval evidence: https://github.com/jselvalugo/DenialDesk/pull/98#issuecomment-5881787399</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>OA-077</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Decide three small things about the sync engine: (a) whether "Sync now" may keep running the whole sync inside the request until background jobs ship (the sandbox takes seconds; a large practice would not fit a serverless time limit); (b) whether a newly synced patient under 18 should get the neutral history note `review_required` (no tag is suggested or set, and no code names minors); (c) whether Coverage-only changes should be searched with `Coverage?_lastUpdated` (built later) or left to the weekly reconciliation in PI3.</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>(a) A run that the platform kills leaves its committed pages and is retried from the old watermark after the 20-minute lease; (b) rationale for a neutral note: the sync-history page is not audited and must hold no PHI, so a code that said "minor" (or named any sensitivity category) would disclose a category of patient outside the audited channels; `review_required` only says a person should look, and the audited patient page is where the reason can be seen (whether minors should also be restricted by default is OA-081); (c) until then a Coverage-only change reaches a patient only when the Patient changes or a payer mapping is saved.</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>A yes/no on (a) and (b), and A or B on (c).</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI2b, "Sync run and issue codes"); OA-056</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>PI2b sync engine builder, 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Before the first real connection</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="n"/>
+      <c r="L77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>OA-078</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Approve an ADR and a re-encryption migration to bind field-level encryption to its record: today the encrypted member ID (and every other encrypted field) has no additional authenticated data (AAD) tying the ciphertext to its row and practice.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>AES-GCM without AAD lets a ciphertext be copied from one row or practice to another and still decrypt. Row-level security and the application's own checks prevent that today, but a database-level mistake or a compromised app role would not be caught by the cipher. Applies app-wide (SSN, MBI, member IDs, bank data), not only to synced patients; the fix needs a format change and re-encrypting every stored value.</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Yes/no and the timing (proposed: before the first real practice). Then an ADR is written and a re-encryption migration built.</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI2b); src/lib/crypto/field.ts; CLAUDE.md non-negotiable 6; R-7.3.3</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>PR #98 review (security M3), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="n"/>
+      <c r="L78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>OA-079</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Confirm that linking a synced patient overwrites a manually entered patient with the same MRN and birth date, including the name, address and member ID the practice typed (and clears the member ID when the EHR coverage is not usable).</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>The spec says an exact MRN and birth-date match links the two; the sync then owns those fields and the practice can no longer edit them. It is the one path by which the EHR can replace practice-entered data, with no human confirmation.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Confirm as built, or ask for a confirmation step (for example an administrator reviews each proposed link) or for keeping the manual member ID when the EHR has none.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI2b upsert and linking); threat model T3, T5</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>PR #98 review (L5), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Before the first real connection</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="n"/>
+      <c r="L79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>OA-080</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Decide whether to store the source's sensitivity category (for example HIV, psychiatric, substance use) or only the `source_restricted` flag.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Today the sync stores the recognized labels in a fixed vocabulary on the patient row (`source_sensitivity`) as well as the flag. A category on a patient row is itself sensitive; the flag alone is enough to restrict, and the category is only needed if masking must differ by category (for example a 42 CFR Part 2 program).</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Keep category and flag, or flag only (and drop `source_sensitivity` in a later migration).</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (field mapping); threat model I4; OA-052</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>PR #98 review (N1), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Before patients P4 masking</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="n"/>
+      <c r="L80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>OA-081</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Decide whether patients under 18 should be restricted by default (masked like a restricted-in-source patient).</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>The sync records only the neutral note `review_required` for a new minor and sets no tag or restriction (a code that named a minor would disclose a category on an unaudited page). Whether minors are treated as sensitive at all is a policy and legal question (Florida minor-consent rules), not a technical one.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Yes (restrict by default), no, or restrict only for services with minor-consent rules, with counsel's reasoning.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (field mapping, birth_date); threat model I4; OA-077(b)</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>PR #98 review (N2), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Before patients P4 masking</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="n"/>
+      <c r="L81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>OA-082</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Accept, or refuse, that restricted-in-source patients are visible to every role in the practice until patients P4 masking ships.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>The sync marks patients restricted (`source_restricted`) but nothing masks them yet, so any staff member who can see the Patient Register sees them. The interim is safe only with synthetic data (pre-production); real data must wait for masking (threat model I4, blocking before real data). With the sync also refusing real connections until PI4, the interim exposes no real patient today.</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Accept the interim for synthetic data only (yes/no), and confirm masking stays a blocker for the first real connection.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md; threat model I4; R-3.5.1, R-4.5.1; OA-052</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>PR #98 review (N3), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Before the first real connection</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="n"/>
+      <c r="L82" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L75"/>
-  <dataValidations count="3">
+  <autoFilter ref="A1:L82"/>
+  <dataValidations count="6">
+    <dataValidation sqref="B10:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
+    </dataValidation>
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
+    <dataValidation sqref="C10:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"P0,P1,P2,P3"</formula1>
+    </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D10:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Data source,Clarification,Decision,Legal/Compliance,Vendor/Account,Design/Brand,Business"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Data source,Clarification,Decision,Legal/Compliance,Vendor/Account,Design/Brand,Business"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$84</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -59,12 +59,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -432,13 +435,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -4894,23 +4900,122 @@
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
     </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>OA-083</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether a claim_imports table (file SHA-256, counts, importer, time) should be added so a re-uploaded charge file is caught by file identity; it needs a new table and a GRANT to denialdesk_app, so it needs your sign-off (R-15.9).</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>C2 charge import detects re-uploads by claim number only, so a file whose claim numbers were all changed is not recognised as the same file.</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Approve or decline the table and its grant; if approved, the retention period for import history.</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C2</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C2 (vigilant-tesla-ps41e9)</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr"/>
+      <c r="L83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>OA-084</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Answer the C2 charge-import questions: (1) who counts as a biller (C2 uses admin, manager, specialist); (2) is a same-patient, same-payer, same-day, same-code-and-modifiers row always a duplicate, or does the practice need an override for a legitimate repeat service; (3) is one claim per Claim number right, or must one PM encounter split into several claims per payer; (4) which practice-management system exports will supply the file, so the columns can be mapped.</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>The import refuses possible duplicates with no override and creates one claim per Claim number; a wrong assumption blocks real charge files.</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Answers to the four questions.</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C2</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C2 (vigilant-tesla-ps41e9)</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L82"/>
-  <dataValidations count="6">
-    <dataValidation sqref="B10:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
-    </dataValidation>
+  <autoFilter ref="A1:L84"/>
+  <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
-    <dataValidation sqref="C10:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"P0,P1,P2,P3"</formula1>
-    </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D10:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Data source,Clarification,Decision,Legal/Compliance,Vendor/Account,Design/Brand,Business"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Data source,Clarification,Decision,Legal/Compliance,Vendor/Account,Design/Brand,Business"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$84</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -4894,8 +4894,116 @@
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>OA-083</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Sign off (R-15.9) on migration 0044 before it runs anywhere beyond a local or test database: it creates the NOLOGIN role `denialdesk_jobs`, two SECURITY DEFINER functions (`integration_claim_run(uuid)`, `integration_enqueue_due_runs()`), and their GRANT and REVOKE statements. Every statement is listed verbatim in the PR description, docs/PROJECT_STATE.md and ADR 0012.</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Background sync jobs need a database role that can do exactly two things: ask whether a run is a queued run of an active connection (and whose), and queue the 15-minute scheduled runs. The role has no table privilege, `denialdesk_app` is not granted either function, and PUBLIC is revoked first. The functions run as their owner and walk the practices one at a time under each practice's own row-level security policy (no policy or BYPASSRLS is added). The same migration also checks that the integration service-principal row seeded by 0043 is still disabled, has the non-hash password marker and no membership (security review L3), and stops the migration if not. Netlify has already applied 0001 to 0043; 0044 is new and pending.</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Approve, or ask for a different shape (for example the claim as a plain function without the tenant walk, which needs a BYPASSRLS or superuser owner). Recorded on the PR.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI2b Jobs, PI3); docs/decisions/0012-background-execution.md; drizzle/0044_patient_integrations_jobs.sql; R-15.9</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>PI2c jobs builder, 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>Before 0044 is merged (Netlify applies migrations on the next deploy)</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="n"/>
+      <c r="L83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>OA-084</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Vendor/Account</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Generate INTEGRATION_JOB_SECRET (at least 32 random bytes, for example `openssl rand -base64 48`) and set it as a functions-only secret in the Netlify site settings, then check that the site's own password protection does not block the function URL the app posts jobs to.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>The secret signs every background sync job (HMAC-SHA256 over the body and a timestamp) and lets the worker refuse forged or replayed ones. Until it is set nothing breaks: Sync now keeps running in the request as before, and the worker and the 15-minute scheduled function refuse to run. Once it is set, Sync now queues a job by posting to this deploy's own `/.netlify/functions/integration-sync-background`, and the site is behind Netlify password protection. If that protection also covers function URLs the post is refused (a 401 from Netlify) and Sync now reports that the sync could not be started; the fix would then be an exemption for that path or a basic-auth header, which is a small follow-up. Scheduled functions run only on the published (production) deploy, not on deploy previews. Never commit the value; production keeps it in Key Vault.</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation the secret is set for functions only (not the build or the client) and never pasted anywhere else; then, after the next deploy, press Sync now on the pre-production sandbox connection and confirm it says the sync was queued and a run appears in Sync history, and that a scheduled run appears within 15 minutes. Tell the agent if the press says it could not be started.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md PI2b Jobs, PI3; docs/decisions/0012-background-execution.md; docs/runbooks/netlify.md; R-7.3.5</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>PI2c jobs builder, 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Before the first background sync on Netlify</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="n"/>
+      <c r="L84" s="2" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L82"/>
+  <autoFilter ref="A1:L84"/>
   <dataValidations count="6">
     <dataValidation sqref="B10:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>agent Claude C2 (vigilant-tesla-ps41e9)</t>
+          <t>agent Claude C2 (vigilant-tesla-ps41e9), 2026-09-29</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>agent Claude C2 (vigilant-tesla-ps41e9)</t>
+          <t>agent Claude C2 (vigilant-tesla-ps41e9), 2026-09-29</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -4977,7 +4977,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>Answer the C2 charge-import questions: (1) who counts as a biller (C2 uses admin, manager, specialist); (2) is a same-patient, same-payer, same-day, same-code-and-modifiers row always a duplicate, or does the practice need an override for a legitimate repeat service; (3) is one claim per Claim number right, or must one PM encounter split into several claims per payer; (4) which practice-management system exports will supply the file, so the columns can be mapped.</t>
+          <t>Answer the C2 charge-import questions: (1) who counts as a biller (C2 uses admin, manager, specialist); (2) is a same-patient, same-payer, same-day, same-code-and-modifiers row always a duplicate, or does the practice need an override for a legitimate repeat service; (3) is one claim per Claim number right, or must one PM encounter split into several claims per payer; (4) which practice-management system exports will supply the file, so the columns can be mapped; (5) can one claim legitimately carry the same line twice (for example the same J-code with different NDCs, or separate-line billing of the same service)? The import refuses a repeated procedure code plus modifiers on one claim, and there is no override yet; (6) is it acceptable that a claim's rows must be next to each other in the file (a claim number that comes back after other claims is refused), or do your PM exports interleave claims? Note: the import rate limit (10 per practice per 10 minutes) counts every attempt, refused ones included.</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Answers to the four questions.</t>
+          <t>Answers to the four questions; answers to (5) and (6), and whether 10 attempts per 10 minutes is enough for a billing day.</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$84</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -59,12 +59,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -432,13 +435,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L82"/>
+  <dimension ref="A1:L84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
@@ -4894,23 +4900,122 @@
       <c r="K82" s="2" t="n"/>
       <c r="L82" s="2" t="n"/>
     </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>OA-083</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether a claim_imports table (file SHA-256, counts, importer, time) should be added so a re-uploaded charge file is caught by file identity; it needs a new table and a GRANT to denialdesk_app, so it needs your sign-off (R-15.9).</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>C2 charge import detects re-uploads by claim number only, so a file whose claim numbers were all changed is not recognised as the same file.</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Approve or decline the table and its grant; if approved, the retention period for import history.</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C2</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C2 (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr"/>
+      <c r="L83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>OA-084</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Answer the C2 charge-import questions: (1) who counts as a biller (C2 uses admin, manager, specialist); (2) is a same-patient, same-payer, same-day, same-code-and-modifiers row always a duplicate, or does the practice need an override for a legitimate repeat service; (3) is one claim per Claim number right, or must one PM encounter split into several claims per payer; (4) which practice-management system exports will supply the file, so the columns can be mapped; (5) can one claim legitimately carry the same line twice (for example the same J-code with different NDCs, or separate-line billing of the same service)? The import refuses a repeated procedure code plus modifiers on one claim, and there is no override yet; (6) is it acceptable that a claim's rows must be next to each other in the file (a claim number that comes back after other claims is refused), or do your PM exports interleave claims? Note: the import rate limit (10 per practice per 10 minutes) counts every attempt, refused ones included.</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>The import refuses possible duplicates with no override and creates one claim per Claim number; a wrong assumption blocks real charge files.</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>Answers to the four questions; answers to (5) and (6), and whether 10 attempts per 10 minutes is enough for a billing day.</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C2</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C2 (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L82"/>
-  <dataValidations count="6">
-    <dataValidation sqref="B10:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
-    </dataValidation>
+  <autoFilter ref="A1:L84"/>
+  <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>
     </dataValidation>
-    <dataValidation sqref="C10:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"P0,P1,P2,P3"</formula1>
-    </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D10:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Data source,Clarification,Decision,Legal/Compliance,Vendor/Account,Design/Brand,Business"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Data source,Clarification,Decision,Legal/Compliance,Vendor/Account,Design/Brand,Business"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$86</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5008,8 +5008,116 @@
       <c r="K84" s="3" t="inlineStr"/>
       <c r="L84" s="3" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>OA-085</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Data source</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Supply the licensed 837P implementation guide (ASC X12 TR3 005010X222A1) and the chosen clearinghouse's 837P companion guide, and answer the C3a claim-level attestations: does the practice hold a signature on file, accept assignment, and hold a release of information for every patient (CLM06 to CLM09)? Confirm the SBR09 claim filing indicator for Medicare Advantage, ERISA self-funded, SMMC, and PIP payers.</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>C3a generates a synthetic (test-indicator T) 837P from knowledge of the guide, not from the guide itself; every row marked VERIFY in specs/claims.md C3a must be cleared before the first real P file, and four payer types are refused until their SBR09 is confirmed.</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>The guide and companion guide (or a written yes/no on each VERIFY row), the four attestation answers, and the SBR09 codes.</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C3a; R-4.1, §8.2</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C3a (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Before C3b</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr"/>
+      <c r="L85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>OA-086</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether the 837P control numbers (ISA13, GS06, ST02) get a dedicated per-practice sequence table; it needs a GRANT to denialdesk_app, so it needs your sign-off (R-15.9). C3a stores the counter as one practice_settings row (existing table and grant) so it needs no GRANT.</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>The practice_settings row works and is atomic, but it is a general key/value table; a dedicated table with no UPDATE path other than the increment function is easier to audit.</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Approve or decline a dedicated table and its grant.</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C3a; R-15.9</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C3a (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Before C3b</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L84"/>
+  <autoFilter ref="A1:L86"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$87</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5008,8 +5008,170 @@
       <c r="K84" s="3" t="inlineStr"/>
       <c r="L84" s="3" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>OA-085</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Sign off (R-15.9) on migrations 0044 and 0045 before they run beyond a local or test database: they create the NOLOGIN role `denialdesk_jobs`, two SECURITY DEFINER functions (`integration_claim_run(uuid)`, `integration_enqueue_due_runs(boolean)`) and their GRANT and REVOKE statements (0045 drops 0044's zero-argument scheduler function and creates its replacement). Every statement is listed verbatim in the PR description, docs/PROJECT_STATE.md and ADR 0012. Also confirm that a Netlify Database preview branch counts as a test database for this rule.</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Background sync jobs need a database role that can do exactly two things: ask whether a run is a queued run of an active connection (and whose), and queue the 15-minute scheduled runs. The role has no table privilege, `denialdesk_app` is not granted either function, and PUBLIC is revoked first. The functions run as their owner and walk the practices one at a time under each practice's own row-level security policy (no policy or BYPASSRLS is added). Both migrations also check that the integration service-principal row seeded by 0043 is still disabled, has the non-hash password marker, no second-factor secret, the reserved address and no membership, and stop the migration if not. IMPORTANT: 0044 has ALREADY been applied to the Netlify preview database branch of PR #100 (deploy previews get their own database branch); Migration 0043 was in the same position (Netlify previews had applied it when it was approved, OA-076). Netlify has applied 0001 to 0043 to the main preview database; 0044 and 0045 are pending there. ⚠️ VERIFY: roles are cluster-wide in PostgreSQL, so a role created on a preview branch might be visible outside that branch depending on how Netlify Database provisions branches; the agent could not confirm that a role created on a preview branch does not reach the shared pre-production database.</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Approve, or ask for a different shape (for example the claim as a plain function without the tenant walk, which needs a BYPASSRLS or superuser owner). Say whether preview database branches count as test databases for R-15.9, and whether the ⚠️ VERIFY about roles reaching the shared pre-production database needs checking in the Netlify Database console before merge. Recorded on the PR.</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI2b Jobs, PI3); docs/decisions/0012-background-execution.md; drizzle/0044_patient_integrations_jobs.sql; drizzle/0045_patient_integrations_jobs_review.sql; R-15.9</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>PI2c jobs builder, 2026-09-29 (revised in the PR #100 review round)</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Before PR #100 is merged (Netlify applies migrations on the next deploy)</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="n"/>
+      <c r="L85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>OA-086</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Vendor/Account</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Generate INTEGRATION_JOB_SECRET (at least 32 random bytes, for example `openssl rand -base64 48`) and set it as a functions-only secret in the Netlify site settings, with a DIFFERENT value per deploy context (Production, and separately Deploy Previews and Branch deploys). Confirm the Netlify plan supports Background Functions, and check that the site's own password protection does not block the function URL the app posts jobs to.</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>The secret signs every background sync job (HMAC-SHA256 over the body and a timestamp) and lets the worker refuse forged or replayed ones. Previews run pull-request code, which can read its own environment, so a value shared with production would let a pull request forge jobs against production. Until it is set nothing breaks: Sync now keeps running in the request as before (only where synthetic data is allowed), and the worker and the 15-minute scheduled function refuse to run. Once it is set, Sync now queues a job by posting to this deploy's own `/.netlify/functions/integration-sync-background`, and the site is behind Netlify password protection. If that protection also covers function URLs the post is refused (a 401 from Netlify) and Sync now reports that the sync could not be started; the fix would then be an exemption for that path or a basic-auth header, a small follow-up. Background Functions (the `-background` suffix) need a plan that includes them. Scheduled functions run only on the published (production) deploy, not on deploy previews. Whether `DEPLOY_URL` or `URL` exist at function and server runtime is also unverified (the runbook lists how to check). Never commit the value; production keeps it in Key Vault.</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Confirmation the secret is set for functions only (not the build or the client), that Production and the preview contexts hold different values, and that the plan supports Background Functions; then, after the next deploy, press Sync now on the pre-production sandbox connection and confirm it says the sync was queued and a run appears in Sync history, and that a scheduled run appears within 15 minutes; and that the deploy log lists both functions. Tell the agent if the press says it could not be started.</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md PI2b Jobs, PI3; docs/decisions/0012-background-execution.md; docs/runbooks/netlify.md; R-7.3.5</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>PI2c jobs builder, 2026-09-29 (revised in the PR #100 review round)</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Before the first background sync on Netlify</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="n"/>
+      <c r="L86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>OA-087</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Confirm that the Netlify Functions region and the Netlify Database region for this site are in the United States, and record where you checked.</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>ADR 0003 leaves this as ⚠️ VERIFY: Netlify is not the HIPAA host and its functions are not restricted to U.S. regions the way the Azure landing zone will be. Until now the Netlify code ran only when a person pressed a button on synthetic data. The 15-minute scheduled function and the background worker now process data unattended there, so Fla. Stat. § 408.051(3) residency should be confirmed even though pre-production holds synthetic data only (CLAUDE.md non-negotiable 3).</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>The region shown in the Netlify site settings for Functions and for the database, or a statement that either cannot be confirmed (then the scheduler should stay off until it can).</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/0003-netlify-preproduction.md; docs/decisions/0012-background-execution.md; CLAUDE.md non-negotiable 3</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>PI2c jobs builder, 2026-09-29 (PR #100 review round)</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>Before enabling the scheduled function on Netlify</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="n"/>
+      <c r="L87" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L84"/>
+  <autoFilter ref="A1:L87"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -5036,12 +5036,12 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Background sync jobs need a database role that can do exactly two things: ask whether a run is a queued run of an active connection (and whose), and queue the 15-minute scheduled runs. The role has no table privilege, `denialdesk_app` is not granted either function, and PUBLIC is revoked first. The functions run as their owner and walk the practices one at a time under each practice's own row-level security policy (no policy or BYPASSRLS is added). Both migrations also check that the integration service-principal row seeded by 0043 is still disabled, has the non-hash password marker, no second-factor secret, the reserved address and no membership, and stop the migration if not. IMPORTANT: 0044 has ALREADY been applied to the Netlify preview database branch of PR #100 (deploy previews get their own database branch); Migration 0043 was in the same position (Netlify previews had applied it when it was approved, OA-076). Netlify has applied 0001 to 0043 to the main preview database; 0044 and 0045 are pending there. ⚠️ VERIFY: roles are cluster-wide in PostgreSQL, so a role created on a preview branch might be visible outside that branch depending on how Netlify Database provisions branches; the agent could not confirm that a role created on a preview branch does not reach the shared pre-production database.</t>
+          <t>Background sync jobs need a database role that can do exactly two things: ask whether a run is a queued run of an active connection (and whose), and queue the 15-minute scheduled runs. The role has no table privilege, `denialdesk_app` is not granted either function, and PUBLIC is revoked first. The functions run as their owner and walk the practices one at a time under each practice's own row-level security policy (no policy or BYPASSRLS is added). Both migrations also check that the integration service-principal row seeded by 0043 is still disabled, has the non-hash password marker, no second-factor secret, the reserved address and no membership, and stop the migration if not. IMPORTANT: 0044 has ALREADY been applied to the Netlify preview database branch of PR #100 (deploy previews get their own database branch); Migration 0043 was in the same position (Netlify previews had applied it when it was approved, OA-076). Netlify has applied 0001 to 0043 to the main preview database; 0044 and 0045 are pending there. ⚠️ VERIFY: roles are cluster-wide in PostgreSQL, so a role created on a preview branch might be visible outside that branch depending on how Netlify Database provisions branches; the agent could not confirm that a role created on a preview branch does not reach the shared pre-production database. ⚠️ VERIFY: that Netlify Database applies each migration.sql in a single transaction. If it does not, PUBLIC briefly holds EXECUTE on a new function between its CREATE FUNCTION and the REVOKE that follows it (in 0044 and 0045); the functions only return identifiers and check their caller's tenant setting, but the window should be known. The agent could not confirm how Netlify runs a migration file.</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>Approve, or ask for a different shape (for example the claim as a plain function without the tenant walk, which needs a BYPASSRLS or superuser owner). Say whether preview database branches count as test databases for R-15.9, and whether the ⚠️ VERIFY about roles reaching the shared pre-production database needs checking in the Netlify Database console before merge. Recorded on the PR.</t>
+          <t>Approve, or ask for a different shape (for example the claim as a plain function without the tenant walk, which needs a BYPASSRLS or superuser owner). Say whether preview database branches count as test databases for R-15.9, and whether the ⚠️ VERIFY about roles reaching the shared pre-production database needs checking in the Netlify Database console before merge. Recorded on the PR. Also whether Netlify Database runs each migration file in one transaction.</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$85</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5008,8 +5008,62 @@
       <c r="K84" s="3" t="inlineStr"/>
       <c r="L84" s="3" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>OA-085</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether refused reveal attempts (member ID on another payer's claim, locked custom fields, wrong role) should write their own audit event such as patient.member_id_reveal_refused.</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Today a refused reveal writes no audit event (nothing is decrypted), unlike refused charge imports and step-ups; auditing it would give SIEM alerting (R-7.5.3) a signal for crafted requests.</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no, and if yes which refusals; the agent adds an IDs-only refusal event and tests.</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>R-5.1.2, R-7.5.1, R-7.5.3; specs/denial-queue.md</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>Claude scheduled review 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Before Azure cutover</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr"/>
+      <c r="L85" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L84"/>
+  <autoFilter ref="A1:L85"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$87</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L84"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5008,8 +5008,170 @@
       <c r="K84" s="3" t="inlineStr"/>
       <c r="L84" s="3" t="inlineStr"/>
     </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>OA-085</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>Sign off (R-15.9) on migrations 0044 and 0045 before they run beyond a local or test database: they create the NOLOGIN role `denialdesk_jobs`, two SECURITY DEFINER functions (`integration_claim_run(uuid)`, `integration_enqueue_due_runs(boolean)`) and their GRANT and REVOKE statements (0045 drops 0044's zero-argument scheduler function and creates its replacement). Every statement is listed verbatim in the PR description, docs/PROJECT_STATE.md and ADR 0012. Also confirm that a Netlify Database preview branch counts as a test database for this rule.</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>Background sync jobs need a database role that can do exactly two things: ask whether a run is a queued run of an active connection (and whose), and queue the 15-minute scheduled runs. The role has no table privilege, `denialdesk_app` is not granted either function, and PUBLIC is revoked first. The functions run as their owner and walk the practices one at a time under each practice's own row-level security policy (no policy or BYPASSRLS is added). Both migrations also check that the integration service-principal row seeded by 0043 is still disabled, has the non-hash password marker, no second-factor secret, the reserved address and no membership, and stop the migration if not. IMPORTANT: 0044 has ALREADY been applied to the Netlify preview database branch of PR #100 (deploy previews get their own database branch); Migration 0043 was in the same position (Netlify previews had applied it when it was approved, OA-076). Netlify has applied 0001 to 0043 to the main preview database; 0044 and 0045 are pending there. ⚠️ VERIFY: roles are cluster-wide in PostgreSQL, so a role created on a preview branch might be visible outside that branch depending on how Netlify Database provisions branches; the agent could not confirm that a role created on a preview branch does not reach the shared pre-production database. ⚠️ VERIFY: that Netlify Database applies each migration.sql in a single transaction. If it does not, PUBLIC briefly holds EXECUTE on a new function between its CREATE FUNCTION and the REVOKE that follows it (in 0044 and 0045); the functions only return identifiers and check their caller's tenant setting, but the window should be known. The agent could not confirm how Netlify runs a migration file.</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>Approve, or ask for a different shape (for example the claim as a plain function without the tenant walk, which needs a BYPASSRLS or superuser owner). Say whether preview database branches count as test databases for R-15.9, and whether the ⚠️ VERIFY about roles reaching the shared pre-production database needs checking in the Netlify Database console before merge. Recorded on the PR. Also whether Netlify Database runs each migration file in one transaction.</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md (PI2b Jobs, PI3); docs/decisions/0012-background-execution.md; drizzle/0044_patient_integrations_jobs.sql; drizzle/0045_patient_integrations_jobs_review.sql; R-15.9</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>PI2c jobs builder, 2026-09-29 (revised in the PR #100 review round)</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>Before PR #100 is merged (Netlify applies migrations on the next deploy)</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="n"/>
+      <c r="L85" s="3" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>OA-086</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Vendor/Account</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Generate INTEGRATION_JOB_SECRET (at least 32 random bytes, for example `openssl rand -base64 48`) and set it as a functions-only secret in the Netlify site settings, with a DIFFERENT value per deploy context (Production, and separately Deploy Previews and Branch deploys). Confirm the Netlify plan supports Background Functions, and check that the site's own password protection does not block the function URL the app posts jobs to.</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>The secret signs every background sync job (HMAC-SHA256 over the body and a timestamp) and lets the worker refuse forged or replayed ones. Previews run pull-request code, which can read its own environment, so a value shared with production would let a pull request forge jobs against production. Until it is set nothing breaks: Sync now keeps running in the request as before (only where synthetic data is allowed), and the worker and the 15-minute scheduled function refuse to run. Once it is set, Sync now queues a job by posting to this deploy's own `/.netlify/functions/integration-sync-background`, and the site is behind Netlify password protection. If that protection also covers function URLs the post is refused (a 401 from Netlify) and Sync now reports that the sync could not be started; the fix would then be an exemption for that path or a basic-auth header, a small follow-up. Background Functions (the `-background` suffix) need a plan that includes them. Scheduled functions run only on the published (production) deploy, not on deploy previews. Whether `DEPLOY_URL` or `URL` exist at function and server runtime is also unverified (the runbook lists how to check). Never commit the value; production keeps it in Key Vault.</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Confirmation the secret is set for functions only (not the build or the client), that Production and the preview contexts hold different values, and that the plan supports Background Functions; then, after the next deploy, press Sync now on the pre-production sandbox connection and confirm it says the sync was queued and a run appears in Sync history, and that a scheduled run appears within 15 minutes; and that the deploy log lists both functions. Tell the agent if the press says it could not be started.</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>docs/specs/patient-integrations.md PI2b Jobs, PI3; docs/decisions/0012-background-execution.md; docs/runbooks/netlify.md; R-7.3.5</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>PI2c jobs builder, 2026-09-29 (revised in the PR #100 review round)</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>Before the first background sync on Netlify</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="n"/>
+      <c r="L86" s="3" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>OA-087</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Confirm that the Netlify Functions region and the Netlify Database region for this site are in the United States, and record where you checked.</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>ADR 0003 leaves this as ⚠️ VERIFY: Netlify is not the HIPAA host and its functions are not restricted to U.S. regions the way the Azure landing zone will be. Until now the Netlify code ran only when a person pressed a button on synthetic data. The 15-minute scheduled function and the background worker now process data unattended there, so Fla. Stat. § 408.051(3) residency should be confirmed even though pre-production holds synthetic data only (CLAUDE.md non-negotiable 3).</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>The region shown in the Netlify site settings for Functions and for the database, or a statement that either cannot be confirmed (then the scheduler should stay off until it can).</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>docs/decisions/0003-netlify-preproduction.md; docs/decisions/0012-background-execution.md; CLAUDE.md non-negotiable 3</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>PI2c jobs builder, 2026-09-29 (PR #100 review round)</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>Before enabling the scheduled function on Netlify</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="n"/>
+      <c r="L87" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L84"/>
+  <autoFilter ref="A1:L87"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$91</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5224,8 +5224,170 @@
       <c r="K88" s="3" t="n"/>
       <c r="L88" s="3" t="n"/>
     </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>OA-089</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Data source</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>Supply the licensed 837P implementation guide (ASC X12 TR3 005010X222A1) and the chosen clearinghouse's 837P companion guide, and answer the C3a claim-level attestations: does the practice hold a signature on file, accept assignment, and hold a release of information for every patient (CLM06 to CLM09)? Confirm the SBR09 claim filing indicator for Medicare Advantage, ERISA self-funded, SMMC, and PIP payers.</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>C3a generates a synthetic (test-indicator T) 837P from knowledge of the guide, not from the guide itself; every row marked VERIFY in specs/claims.md C3a must be cleared before the first real P file, and four payer types are refused until their SBR09 is confirmed.</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>The guide and companion guide (or a written yes/no on each VERIFY row), the four attestation answers, and the SBR09 codes.</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C3a; R-4.1, §8.2</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C3a (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>Before C3b</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="n"/>
+      <c r="L89" s="3" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>OA-090</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether the 837P control numbers (ISA13, GS06, ST02) get a dedicated per-practice sequence table; it needs a GRANT to denialdesk_app, so it needs your sign-off (R-15.9). C3a stores the counter as one practice_settings row (existing table and grant) so it needs no GRANT.</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>The practice_settings row works and is atomic, but it is a general key/value table; a dedicated table with no UPDATE path other than the increment function is easier to audit.</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Approve or decline a dedicated table and its grant.</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C3a; R-15.9</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C3a (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>Before C3b</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="n"/>
+      <c r="L90" s="3" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>OA-091</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Answer three C3a compliance questions with counsel: (1) does DenialDesk become a HIPAA health care clearinghouse by generating standard transactions (837P) for practices, and what follows; (2) how are 42 CFR Part 2 consent and sensitivity-tagged diagnoses handled on outgoing claims; (3) may real claim files ever be downloaded to a person's device, or only sent to the clearinghouse.</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>C3a already builds and offers a download of the 837P (synthetic only). These answers gate C3b and any real claim.</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>Counsel answers or a decision on each of the three.</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C3a; R-3.5.1, R-3.5.2, R-4.1</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C3a (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>Before C3b</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="n"/>
+      <c r="L91" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L87"/>
+  <autoFilter ref="A1:L91"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$92</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5386,8 +5386,62 @@
       <c r="K91" s="3" t="n"/>
       <c r="L91" s="3" t="n"/>
     </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>OA-092</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Data source</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Supply the CMS place of service (POS) code set, and tell us which codes the practice bills from each location, so the Billing settings page can check a code against the real list. Today it checks only that the code is two digits.</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>A wrong POS code changes how a payer prices and pays the claim. The page (specs/claims.md C3a-S) and the 837P generator check the format only, and DenialDesk does not state what a code means without a source.</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>The CMS POS code set file (or the link the practice uses) and, per location, the code it bills with.</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C3a-S; R-4.1</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C3a-S (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>Before C3b</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="n"/>
+      <c r="L92" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L91"/>
+  <autoFilter ref="A1:L92"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -4653,7 +4653,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Approve an ADR and a re-encryption migration to bind field-level encryption to its record: today the encrypted member ID (and every other encrypted field) has no additional authenticated data (AAD) tying the ciphertext to its row and practice. Proposed design: ADR 0011 (docs/decisions/0011-field-encryption-aad-envelope-v2.md, PR #97) with spec docs/specs/field-encryption-aad.md; also answer spec questions 2-5: run the re-encryption job on pre-production or wipe and re-seed (security review recommends re-seed); who confirms the legacy cut-off; confirm Azure production starts empty; whether the pre-production FIELD_ENCRYPTION_KEY was ever changed.</t>
+          <t>Approve an ADR and a re-encryption migration to bind field-level encryption to its record: today the encrypted member ID (and every other encrypted field) has no additional authenticated data (AAD) tying the ciphertext to its row and practice. Proposed design: ADR 0011 (docs/decisions/0011-field-encryption-aad-envelope-v2.md, PR #97) with spec docs/specs/field-encryption-aad.md; also answer spec questions 2-5 and 12: run the re-encryption job on pre-production or wipe and re-seed (security review recommends re-seed); who confirms the legacy cut-off; confirm Azure production starts empty; whether the pre-production FIELD_ENCRYPTION_KEY was ever changed; whether production refuses legacy (v1) provider TINs.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Approval of ADR 0011 (or requested changes) and the timing; answers to spec questions 2-5.</t>
+          <t>Approval of ADR 0011 (or requested changes) and the timing; answers to spec questions 2-5 and 12.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$96</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5440,8 +5440,224 @@
       <c r="K92" s="3" t="n"/>
       <c r="L92" s="3" t="n"/>
     </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>OA-093</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Clarification</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether Spanish and Portuguese payer-facing appeal letter templates are needed, and whether template edits need their own version history.</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>A letter goes to the payer, so A2 ships English templates only (the UI around them is en/es/pt). A template history table would need a new GRANT (R-15.9).</t>
+        </is>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no per language; yes/no for template history.</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>specs/appeals.md A2; R-7.11.2</t>
+        </is>
+      </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude A2 (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>Before A3</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>OA-094</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether an exported appeal letter may show the full member ID (decrypted at print time, audited) or only the last four characters.</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>Payers often need the full ID. A2 masks it (minimum necessary, HC-3.3; field-level encryption, R-7.3.3) and the biller types the full ID after the audited reveal on the appeal page.</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Keep masked, or allow the full ID on the print view only.</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>specs/appeals.md A2; HC-3.3; R-7.3.3</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude A2 (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>Before real data</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>OA-095</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>Decide where a payer's appeals mailing address and fax number should live so letters can merge them (a new column on payers, or a per-appeal field).</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>The payers table has no address column, so starter letters carry a fill-in placeholder for it. A new column needs a migration.</t>
+        </is>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>Choice of location and where the addresses come from.</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>specs/appeals.md A2; specs/payer-catalog.md</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude A2 (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>Before A3</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>OA-096</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Confirm who may attest and export appeal letters (built: admin, manager, specialist; compliance read-only), whether a second person must review a letter the author wrote, and whether recording a submission should require an attestation.</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>R-7.11.2 requires a named user to approve before anything reaches a payer. A2 blocks export without an attestation but does not require four eyes or gate 'record submission'.</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>A decision on each of the three.</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>specs/appeals.md A2; R-7.11.2, R-5.1.2</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude A2 (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>Before A3</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L91"/>
+  <autoFilter ref="A1:L96"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$94</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5494,8 +5494,62 @@
       <c r="K93" s="3" t="n"/>
       <c r="L93" s="3" t="n"/>
     </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>OA-097</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether changing a provider's billing name or address (not only the TIN) should also require a fresh step-up MFA on Settings &gt; Billing.</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>They go on every claim, so a wrong address misdirects payment. C3a-S asks for the step-up only when the TIN is set or changed, to keep the page usable.</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Yes or no, and if yes which fields.</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>specs/claims.md C3a-S; R-7.2.2, HC-4.2</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude C3a-S (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>Before launch</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L93"/>
+  <autoFilter ref="A1:L94"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$97</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5389,7 +5389,7 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>OA-101</t>
+          <t>OA-092</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -5404,37 +5404,37 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Legal/Compliance</t>
+          <t>Data source</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>Decide whether local development may keep Next.js's unavoidable 'next dev' update check (it asks registry.npmjs.org for newer Next.js versions; no opt-out in 16.3.6) under a written, time-boxed exception ADR signed by the Security and Privacy Officers (HC §0), or keep SC-A2.6 tracked as a known gap.</t>
+          <t>Supply the CMS place of service (POS) code set, and tell us which codes the practice bills from each location, so the Billing settings page can check a code against the real list. Today it checks only that the code is two digits.</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>SC-A2.6 bans update checks; everything else that phones home is now off. No PHI is involved (local development holds synthetic data only).</t>
+          <t>A wrong POS code changes how a payer prices and pays the claim. The page (specs/claims.md C3a-S) and the 837P generator check the format only, and DenialDesk does not state what a code means without a source.</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>Accept (officers sign an exception ADR the agent drafts) or keep tracked.</t>
+          <t>The CMS POS code set file (or the link the practice uses) and, per location, the code it bills with.</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>SC-A2.6; HC §0; PR #96</t>
+          <t>specs/claims.md C3a-S; R-4.1</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>SC gap PRs session 2026-09-29</t>
+          <t>agent Claude C3a-S (vigilant-tesla-ps41e9), 2026-09-29</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>Before the first real practice</t>
+          <t>Before C3b</t>
         </is>
       </c>
       <c r="K92" s="3" t="n"/>
@@ -5443,7 +5443,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>OA-102</t>
+          <t>OA-097</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -5463,32 +5463,32 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Approve a separate RATE_LIMIT_HASH_KEY so src/lib/rate-limit.ts stops reusing FIELD_ENCRYPTION_KEY as a hash salt (spec question 6).</t>
+          <t>Decide whether changing a provider's billing name or address (not only the TIN) should also require a fresh step-up MFA on Settings &gt; Billing.</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>One key per purpose; rotating the field key must not reset rate-limit windows.</t>
+          <t>They go on every claim, so a wrong address misdirects payment. C3a-S asks for the step-up only when the TIN is set or changed, to keep the page usable.</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>Yes/no; if yes the agent adds the variable in a follow-up PR (never the value in the sheet).</t>
+          <t>Yes or no, and if yes which fields.</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1; R-7.3.4; docs/specs/field-encryption-aad.md</t>
+          <t>specs/claims.md C3a-S; R-7.2.2, HC-4.2</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+          <t>agent Claude C3a-S (vigilant-tesla-ps41e9), 2026-09-29</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>Before the first key rotation</t>
+          <t>Before launch</t>
         </is>
       </c>
       <c r="K93" s="3" t="n"/>
@@ -5497,7 +5497,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>OA-103</t>
+          <t>OA-101</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -5507,42 +5507,42 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Legal/Compliance</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Decide the ADR 0011 follow-ups (spec questions 7-10): keep retired keys decrypt-only for append-only custom-field history and synced patients or approve a re-encryption path (R-15.9); key retirement: backup and point-in-time retention periods, no key destruction until legal hold exists, and Security plus Privacy Officer sign-off to destroy a key; run one pre-production key-rotation drill after the cut-off; whether an 835 or find-by-member-ID feature gets a tenant-keyed blind index.</t>
+          <t>Decide whether local development may keep Next.js's unavoidable 'next dev' update check (it asks registry.npmjs.org for newer Next.js versions; no opt-out in 16.3.6) under a written, time-boxed exception ADR signed by the Security and Privacy Officers (HC §0), or keep SC-A2.6 tracked as a known gap.</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Shapes the Azure-cutover key rotation ADR and any member-ID matching feature.</t>
+          <t>SC-A2.6 bans update checks; everything else that phones home is now off. No PHI is involved (local development holds synthetic data only).</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>An answer to each of the four (rotation path, key retirement policy, drill, blind index); the rotation parts can wait for the cutover ADR.</t>
+          <t>Accept (officers sign an exception ADR the agent drafts) or keep tracked.</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1; R-7.3.4; R-15.9; docs/specs/field-encryption-aad.md</t>
+          <t>SC-A2.6; HC §0; PR #96</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+          <t>SC gap PRs session 2026-09-29</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Azure cutover</t>
+          <t>Before the first real practice</t>
         </is>
       </c>
       <c r="K94" s="3" t="n"/>
@@ -5551,7 +5551,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>OA-104</t>
+          <t>OA-102</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -5571,39 +5571,147 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Decide whether rcm_claim_lines.account_number (the practice's patient account number in revenue-cycle files) is field-encrypted like member IDs.</t>
+          <t>Approve a separate RATE_LIMIT_HASH_KEY so src/lib/rate-limit.ts stops reusing FIELD_ENCRYPTION_KEY as a hash salt (spec question 6).</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>HC-7.3/R-7.3.3 list only SSN, MBI, member IDs, and bank data, so plaintext breaks no MUST rule today; it is still an HC-1.1 identifier protected only by at-rest encryption and RLS.</t>
+          <t>One key per purpose; rotating the field key must not reset rate-limit windows.</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Yes/no from the Security and Privacy Officers; if yes, the agent adds it to the ADR 0011 build.</t>
+          <t>Yes/no; if yes the agent adds the variable in a follow-up PR (never the value in the sheet).</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1; HC-1.1; HC-7.3; ADR 0011; docs/specs/field-encryption-aad.md</t>
+          <t>SC-B7.1; R-7.3.4; docs/specs/field-encryption-aad.md</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1 AAD plan session 2026-09-29</t>
+          <t>SC-B7.1 AAD plan session 2026-09-28</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>Before the first real practice</t>
+          <t>Before the first key rotation</t>
         </is>
       </c>
       <c r="K95" s="3" t="n"/>
       <c r="L95" s="3" t="n"/>
     </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>OA-103</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>Decide the ADR 0011 follow-ups (spec questions 7-10): keep retired keys decrypt-only for append-only custom-field history and synced patients or approve a re-encryption path (R-15.9); key retirement: backup and point-in-time retention periods, no key destruction until legal hold exists, and Security plus Privacy Officer sign-off to destroy a key; run one pre-production key-rotation drill after the cut-off; whether an 835 or find-by-member-ID feature gets a tenant-keyed blind index.</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>Shapes the Azure-cutover key rotation ADR and any member-ID matching feature.</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>An answer to each of the four (rotation path, key retirement policy, drill, blind index); the rotation parts can wait for the cutover ADR.</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1; R-7.3.4; R-15.9; docs/specs/field-encryption-aad.md</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>Azure cutover</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="n"/>
+      <c r="L96" s="3" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>OA-104</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether rcm_claim_lines.account_number (the practice's patient account number in revenue-cycle files) is field-encrypted like member IDs.</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>HC-7.3/R-7.3.3 list only SSN, MBI, member IDs, and bank data, so plaintext breaks no MUST rule today; it is still an HC-1.1 identifier protected only by at-rest encryption and RLS.</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no from the Security and Privacy Officers; if yes, the agent adds it to the ADR 0011 build.</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1; HC-1.1; HC-7.3; ADR 0011; docs/specs/field-encryption-aad.md</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1 AAD plan session 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="n"/>
+      <c r="L97" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L95"/>
+  <autoFilter ref="A1:L97"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$102</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -515,4390 +515,4390 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>OA-001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Rename the default branch to `main` and turn on branch protection.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Required control before more PRs land.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Confirmation it is done.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>R-7.4.4</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="3" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>OA-002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Set budget, timeline, team, and success targets.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Scopes the roadmap and what 'best in the world' is measured by.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Filled TODOs in PRODUCT_BRIEF.md.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>docs/PRODUCT_BRIEF.md</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>OA-003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Vendor/Account</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Choose the clearinghouse and open a sandbox account.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Blocks 837P submission and 999/277CA/835 intake (C3, C4).</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Vendor name, companion guides, sandbox access set up by owner.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>specs/claims.md</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Before C3</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>OA-004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Engage healthcare counsel and get the regulatory role memo.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Defines business-associate duties and product limits.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Memo or counsel contact.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ROADMAP Phase 0</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Before real data</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>OA-005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Data source</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Provide verified payer list with EDI payer IDs and regimes (commercial/HMO/Medicaid/Medicare).</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>Unverified payers get no computed deadlines and cannot be billed.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Spreadsheet of payers + source (payer sheet, clearinghouse list).</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>specs/payer-catalog.md</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Before C3</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>OA-006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Decide which Florida timely-filing exceptions (§ 627.6131(2)) the submission block must honor; confirm Medicare Advantage windows come from contracts.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Filing block logic depends on it.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Answer, ideally with counsel citation.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>specs/claims.md</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Before C3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>OA-007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Data source</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>Provide PIP, workers' comp, and Medicaid filing rules and the HMO timely-filing citation.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>Rules engine cannot encode unverified deadlines.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Citations or source documents.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>specs/claims.md; rules/</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Before C3</t>
         </is>
       </c>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>OA-008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Data source</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Decide whether real sample 835 remits/denial letters will ever be used (default: synthetic only); if yes, counsel-approved de-identification and an intake path first.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Improves CARC/RARC classification and appeal drafting quality.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Decision only. Never commit samples or attach them to this sheet.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>R-3.1</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
+      <c r="K9" s="3" t="n"/>
+      <c r="L9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>OA-009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Deposits: accept that the DB owner role can modify deposit rows, or require a guard trigger.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Closes an audit-integrity gap.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Accept / add trigger.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>threat-models/revenue-cycle-imports.md</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>OA-010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Rewrite git history to remove the reference prototype's and competitor names, or leave it.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>IP/brand hygiene; rewrite requires a force-push.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>Rewrite / leave.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>PROJECT_STATE open questions</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>OA-011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Should front-desk registration be its own role? Guarantor now or with statements?</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>Shapes patient module P2 permissions and data model.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>Yes/no for each.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>specs/patients.md</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Before P2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
+      <c r="K12" s="3" t="n"/>
+      <c r="L12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>OA-012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Decide Part 2 consent handling before any SUD-tagged data; confirm address/phone requirements.</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>Required before sensitive data is stored.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>Decision with counsel input.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>R-3.5.1, R-3.5.2</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Before real data</t>
         </is>
       </c>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>OA-013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Counsel review of look and feel (trade dress) before public launch.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>Reduces IP risk on UI chrome kept by ADR 0005.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>Counsel sign-off or change list.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>ADR 0005</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>OA-014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Accountant to confirm net-revenue presentation (write-offs vs. GAAP price concessions) and chart of accounts.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Statements page is labelled 'management view' until then.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Accountant sign-off.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Revenue cycle</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
+      <c r="K15" s="3" t="n"/>
+      <c r="L15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>OA-015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Confirm Azure U.S. regions for production cutover.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Data residency (Fla. Stat. § 408.051(3)).</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Region names.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>ADR 0002</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Before cutover</t>
         </is>
       </c>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
+      <c r="K16" s="3" t="n"/>
+      <c r="L16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>OA-016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Design/Brand</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Get a vector (SVG) logo from a designer.</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>Sharp branding at every size.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>SVG file + license.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>docs/DESIGN.md</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>OA-017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Design/Brand</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Confirm license and generating tool for the sign-in reception image.</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>IP compliance for owner-supplied asset.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>License text / tool name.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>public/brand/README.md</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
+      <c r="K18" s="3" t="n"/>
+      <c r="L18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>OA-018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>Line up 3–5 Florida practices for discovery interviews and a pilot.</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Real workflows and denial mix make the product best-in-class.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>Pointer to where contacts are kept outside the repo (e.g. CRM); no names here.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>docs/PRODUCT_BRIEF.md</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Phase 2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>OA-019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Vendor/Account</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Decide on licensing for CARC/RARC/CPT code sets (X12, AMA).</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Code descriptions shown in-app need proper licenses.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>License decision / accounts.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>R-15.7</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
+      <c r="K20" s="3" t="n"/>
+      <c r="L20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>OA-020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Start SOC 2 Type I readiness (auditor shortlist).</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Enterprise buyers will ask for it.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Auditor choice and target date.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>SOC 2</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-26</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>Post-launch</t>
         </is>
       </c>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
+      <c r="K21" s="3" t="n"/>
+      <c r="L21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>OA-021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Confirm (or have a biller/counsel confirm) how each CARC maps to a denial category, and which adjustments count as denials versus expected reductions (DenialDesk treats PR and CO-45 as expected).</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>Remittance posting now captures denials automatically; the category drives the work queue and appeal routing.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>Reviewed CARC → category table (src/domain/carc.ts) and the expected-adjustment list, with source.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>R-3.10.1, specs/remittances-and-prompt-pay.md (R2)</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>agent R2 2026-09-26</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>Before real remittances</t>
         </is>
       </c>
-      <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="n"/>
+      <c r="K22" s="3" t="n"/>
+      <c r="L22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>OA-022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Confirm how late-payment interest should start (payment due date) and whether it accrues on claims still unpaid.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Prompt-pay interest worksheet and totals depend on it (currently pending counsel verification).</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>Counsel answer with citation (§ 627.6131 interest subsection).</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>R-3.1.3, rules/prompt-pay.ts</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>agent R2 2026-09-26</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Before production</t>
         </is>
       </c>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
+      <c r="K23" s="3" t="n"/>
+      <c r="L23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>OA-023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Confirm whether a late appeal submission (past the computed deadline) should be blocked, warned, or only recorded and flagged.</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>A1 records and flags; a human should confirm this before A2/A3 lock in stricter behavior.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>Decision: block / warn / record-and-flag (current default).</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>specs/appeals.md</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>appeals A1 agent</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>Before A2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
+      <c r="K24" s="3" t="n"/>
+      <c r="L24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>OA-024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Confirm the withdrawn/dismissed decision outcome's mapping to a denial status (A1 default: both set the denial to 'closed' with a required reason).</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>A withdrawal for a procedural reason may need to stay distinguishable from a dismissal on the merits.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Decision to keep the A1 default or add a distinct denial status/flag.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>specs/appeals.md</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>appeals A1 agent</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>Before A2/A3</t>
         </is>
       </c>
-      <c r="K25" s="2" t="n"/>
-      <c r="L25" s="2" t="n"/>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>OA-025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>Decide if an appeal needs its own immutable version history (like claim_versions) once A2 adds an editable letter body.</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>Shapes whether A2 needs a new history table before shipping editable letter content.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>Yes/no decision.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>specs/appeals.md</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>appeals A1 agent</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>Before A2</t>
         </is>
       </c>
-      <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
+      <c r="K26" s="3" t="n"/>
+      <c r="L26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>OA-026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Data source</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Provide a source and an annual-update owner for Medicare appeal amount-in-controversy thresholds (REQUIREMENTS §4.2, QIC/ALJ/Council/federal court).</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>rules/catalog.ts cannot encode the higher Medicare appeal levels' thresholds without a cited source.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Citation/source + who keeps it current.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>specs/appeals.md; rules/</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>appeals A1 agent</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Before A3</t>
         </is>
       </c>
-      <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
+      <c r="K27" s="3" t="n"/>
+      <c r="L27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>OA-027</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Confirm whether any role/field visibility rule beyond the existing claim/denial matrix should mask an appeal's tracking_reference or recovered_cents.</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Confirms R-5.1.2 coverage extends correctly to the new appeal fields.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>Yes/no per field, or 'no change'.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>specs/appeals.md; R-5.1.2</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>appeals A1 agent</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>Before A2</t>
         </is>
       </c>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
+      <c r="K28" s="3" t="n"/>
+      <c r="L28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>OA-028</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Confirm whether a draft (or in_review/ready) appeal that's never submitted can be abandoned/withdrawn, or must always move to submitted before it can be closed out.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>The A1 status trigger only allows withdrawn/dismissed from submitted or awaiting_decision; an abandoned draft currently has no exit path.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Decision: add a draft-cancel transition, or confirm drafts must always be submitted or left open.</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>specs/appeals.md</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>appeals A1 review</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>Before A2</t>
         </is>
       </c>
-      <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
+      <c r="K29" s="3" t="n"/>
+      <c r="L29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>OA-029</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Confirm compliance's read-only role on appeals still permits full member-ID reveal, consistent with (or overriding) the same open question on denials/claims (R-5.1.2).</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Appeals reuse the denial/claim role matrix; an unresolved compliance-visibility decision there also applies here.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>Decision: compliance sees masked-only, or full reveal like other roles.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>specs/appeals.md; R-5.1.2</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>appeals A1 review</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>Before real data</t>
         </is>
       </c>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>OA-030</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Counsel sign-off on the Medicare appeal-level rules added for levels 2-5: the 5-day receipt presumption applied to QIC/ALJ/Council/federal court (not yet confirmed for those levels the way it is for redetermination), the federal-court citation (42 CFR 405.1132 vs 405.1136(c)), and the amount-in-controversy thresholds (42 CFR 405.1006, currently unsourced).</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>All of rules/catalog.ts's levels 2-5 rules are flagged VERIFY; A3 cannot compute a level 2-5 deadline for real practices without this.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Confirmed citations/values, or corrections, per rule ID.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>rules/catalog.ts; rules/deadlines.ts</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>appeals A1 review</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Before A3</t>
         </is>
       </c>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>OA-031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Decide whether sensitivity-tag masking (HIV, SUD/Part 2, etc.) should be enforced on the appeal and denial detail pages now, or deferred with the rest of the sensitivity-tag work (R-3.5.1).</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Appeals show the same patient/claim fields as denials, which don't yet enforce sensitivity tags.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>Decision: enforce now (adds scope to A2) or defer (tracked with the existing sensitivity-tag gap).</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>specs/appeals.md; R-3.5.1</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>appeals A1 review</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>Before real data</t>
         </is>
       </c>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
+      <c r="K32" s="3" t="n"/>
+      <c r="L32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>OA-032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Confirm the retention period for appeal records (appeals, appeal_notes) once a real retention policy exists.</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>No retention/legal-hold policy is defined yet for the new tables, same gap as claims/denials.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>Retention period or pointer to the practice's policy.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>specs/appeals.md</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>appeals A1 review</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>Before real data</t>
         </is>
       </c>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
+      <c r="K33" s="3" t="n"/>
+      <c r="L33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>OA-033</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Confirm whether practices need a written handling/retention policy for downloaded Insight .xlsx report exports.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Exported workbooks leave the audited system as files on a user's device; owner said 'not sure, let's confirm' on 2026-09-26. GATES PRODUCTION: Insight export must not be enabled for a real (Azure) practice tenant until this is answered (docs/PROJECT_STATE.md).</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>Yes/no decision, and policy text or pointer if yes.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>R-9.2.1, SOC 2 C1.1/CC6.7; specs/insight-standard-reports.md</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>insights-standard-reports session 2026-09-26</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>Before enabling Insight export in production (Azure)</t>
         </is>
       </c>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
+      <c r="K34" s="3" t="n"/>
+      <c r="L34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>OA-034</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Have Florida healthcare counsel confirm the deadline-computation readings now encoded in rules/: (1) whether Fla. R. Gen. Prac. &amp; Jud. Admin. 2.514 weekend/holiday roll-forward applies to prompt-pay and timely-filing clocks outside court, and which Florida holiday list governs (§ 110.117 vs § 683.01); (2) the meaning of 'month' under Fla. Stat. § 1.01 and end-of-month clamping (Aug 31 + 6 months = Feb 28/29); (3) date of service vs date of discharge as the timely-filing anchor for inpatient claims; (4) that Medicare Advantage is outside Florida prompt pay (plan contract; 42 CFR 422.520 30-day clean-claim rule for non-contracted providers); (5) interest starting the first calendar day after the prompt-pay deadline; (6) Medicare 1-year filing with next-federal-workday roll-forward. (7) accept or reject the engineering choice (not an owner decision) to apply the reading attributes anchor, rollForward, side and confirmedBy, and the FL insurer/HMO split, to the baseline rule versions instead of adding new effective-dated versions. Until (1) is confirmed, the owner chose option 1 (2026-09-27): the unrolled date governs for provider-side and payer-side deadlines; the rolled date is shown as 'pending counsel' only. After confirmation a human adds a confirmed version to ROLL_FORWARD_POLICY in rules/roll-forward.ts.</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>Every computed deadline on the claims, denials and prompt-pay pages depends on these readings; all stay VERIFY until confirmed.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>Counsel answer per item with citation; then a human records confirmedBy on each rule.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>R-15.6, R-3.1.1, R-3.1.3, R-3.1.5, R-4.2.1, specs/rules-engine-skeleton.md</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>florida-rules-engine 2026-09-26</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Before production</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>2026-09-27: option 1 chosen (conservative/unrolled date governs until counsel confirms roll-forward).</t>
         </is>
       </c>
-      <c r="L35" s="2" t="n"/>
+      <c r="L35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>OA-035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Decide whether DenialDesk University lesson completions should serve as HIPAA training evidence for practices, and in what form (per-user table under Settings, .xlsx export).</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Sets the scope of University U3 (practice training record) and whether it counts toward R-10.4.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>Yes/no, the practice roles who may see it, and any required fields (e.g. annual re-take).</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>R-10.4; specs/denialdesk-university.md U3</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>university session 2026-09-27</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>Before U3</t>
         </is>
       </c>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
+      <c r="K36" s="3" t="n"/>
+      <c r="L36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>OA-036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Decide the structure of the University beyond courses and the Wiki (role-based tracks, knowledge checks, training records, or something else).</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>The Wiki shipped beside the U1 courses; further University work is deliberately unbuilt until the owner shapes it.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>A short outline of the University's sections and what a practice user should be able to do in each.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>docs/specs/university-wiki.md, docs/specs/denialdesk-university.md, R-10.4</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-27</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>Before the next University feature</t>
         </is>
       </c>
-      <c r="K37" s="2" t="n"/>
-      <c r="L37" s="2" t="n"/>
+      <c r="K37" s="3" t="n"/>
+      <c r="L37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>OA-037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Design/Brand</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Confirm the license and generating tool for the DenialDesk Wiki wordmark (public/brand/denialdesk-wiki.png) and the University of DenialDesk logo (public/brand/university-of-denialdesk.png), and that DenialDesk holds the rights to use the logo mark in them.</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Both logos are shown in the header on every signed-in screen and on the welcome page; their provenance is unrecorded (same open question as the reception image).</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>License/rights confirmation and the tool used for each, noted in public/brand/README.md.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>docs/specs/university-wiki.md, docs/specs/denialdesk-university.md, DESIGN.md §4, public/brand/README.md</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-27</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
+      <c r="K38" s="3" t="n"/>
+      <c r="L38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>OA-038</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Ask counsel whether calling the training center "University of DenialDesk" / "DenialDesk University" is permitted under Florida rules on the use of "university" in a name (Fla. Stat. ch. 1005, Commission for Independent Education) or needs a different name before launch.</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>The name appears in the app header, welcome page, and user menu; renaming later would touch the logo, copy, and URLs.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Counsel's answer; if a rename is needed, the new name.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>specs/denialdesk-university.md; public/brand/README.md</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>compliance-checker 2026-09-27</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
+      <c r="K39" s="3" t="n"/>
+      <c r="L39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>OA-040</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Should a practice administrator be able to set a practice-wide default language (English/Spanish/Portuguese) for new users?</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>Today each user gets the browser language until they pick one in the user menu; a practice with mostly Spanish-speaking staff might want Spanish as the starting point.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>Yes/no; if yes, where it is set (Settings &gt; General) and whether users may override it (recommended: yes).</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>R-11.1; specs/internationalization.md</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>internationalization session 2026-09-27</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>Before general availability</t>
         </is>
       </c>
-      <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
+      <c r="K40" s="3" t="n"/>
+      <c r="L40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>OA-041</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Native-speaker review of the Spanish and Portuguese billing terminology (glossary in specs/internationalization.md), plus counsel/compliance sign-off that translated attestations and caveats (synthetic-data attestation, BAA recording labels, uncontestable-obligation alert, R-8.7 suppression and residual-risk text) mean the same thing in law. Added with Submit (PR #88): the Spanish and Portuguese U.S.-residency attestation an administrator ticks before submitting a real EHR connection (`submit.attestation`, `submit.attestationHint`, `error.attestationRequired` in src/i18n/messages/es|pt/integrations.ts) are agent-written and need native-speaker review and counsel sign-off that they mean the same as the English text ("This EHR/PM endpoint stores and processes data only in the United States"). The audit event records the displayed language, the wording version, and a SHA-256 of the exact text shown, so a changed translation needs a version bump.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>The agent-authored translations use U.S. Spanish and Brazilian Portuguese billing vocabulary (reclamación / reivindicação, denegación / negativa, apelación / recurso, remesa / remessa). A biller who works in those languages should confirm the terms, and counsel should confirm the legally operative copy, before real practices see it.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>Confirmed or corrected glossary rows; any screen wording to change; counsel sign-off on the listed copy. For the attestation keys: confirmed or corrected es/pt wording and counsel sign-off (a change means bumping US_RESIDENCY_ATTESTATION_VERSION).</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>R-11.1; specs/internationalization.md</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>internationalization session 2026-09-27</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>Before the first real connection</t>
         </is>
       </c>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>OA-042</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Translate DenialDesk University course lessons and Wiki articles into Spanish and Portuguese?</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>The University UI (navigation, buttons, badges, search) is translated with the rest of the product; the ~1,500 lines of lesson and article content (legal-adjacent educational text with rule tokens) stayed English in PR #64. Translating it is a content project that needs the same counsel/native-speaker review as OA-041.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>Yes/no, and if yes, whether counsel reviews the translated lessons before they ship.</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>R-11.1, R-10.4; specs/internationalization.md, specs/denialdesk-university.md</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>internationalization session 2026-09-27</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>Owner decision; not blocking</t>
         </is>
       </c>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
+      <c r="K42" s="3" t="n"/>
+      <c r="L42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>OA-043</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Confirm the patient list may show sex and city/state beside name, MRN and date of birth (minimum necessary), and whether restricted (sensitivity-tagged) rows should keep hiding them.</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>Compliance-checker flagged the new list columns (record pattern P1) as a minimum-necessary question; the list hides them for tagged rows until decided.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Keep / drop each column; keep or lift the restricted-row rule.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>specs/record-pages.md; 45 CFR 164.502(b)</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>record-pages session 2026-09-27</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>OA-044</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Define the DenialDesk University offer: what "starting at $299" covers (term, renewals, higher tiers), how a practice pays (today the operator records the purchase by hand on the practice page after a request), and who at DenialDesk watches for access requests.</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>Decided 2026-09-27: courses are locked until the operator grants access. Without payment terms and an owner of the request queue, requests can sit unseen and the price shown has no defined scope.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>Pricing terms, the payment/ordering process, and the person who reviews requests in the console.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>specs/denialdesk-university.md (Access); src/domain/university/offer.ts</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>university session 2026-09-27</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>OA-045</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Decide with counsel whether an administrator's U.S.-hosting attestation for the practice's EHR endpoint is enough, or whether DenialDesk must get written confirmation from the EHR vendor; confirm the customer BAA covers DenialDesk pulling patient data from the practice's EHR. Also decide, from the PI2a Submit compliance review: (N3) whether a later migration should add a time floor to the Submit stamps (`submitted_at` and `us_residency_attested_at` must be at least `transaction_timestamp()`, so an app-role writer can't back-date or forward-date them) and, optionally, require `us_residency_attested_by = submitted_by` (attested_by being non-null is already enforced by the 0039 CHECKs); due before the first real connection or the Azure cutover, whichever is first. (N6) Whether the attestation should also name backups and disaster-recovery copies and say the endpoint is "accessed only from the United States"; any change to the wording is a new attestation version (US_RESIDENCY_ATTESTATION_VERSION) and needs new es/pt text (OA-041).</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Fla. Stat. § 408.051(3) data residency and the BAA scope gate every real EHR connection.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Counsel answer: attestation vs. vendor letter, and BAA wording if a change is needed. N3: yes/no on the stamp time floor and on attested_by = submitted_by. N6: the final wording, or confirmation that the current wording stands.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-045); R-3.3.1</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>Before first real connection (N3: also before the Azure cutover)</t>
         </is>
       </c>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
+      <c r="K45" s="3" t="n"/>
+      <c r="L45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>OA-046</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Decide whether to retire manual patient registration once a practice's EHR is connected, and what happens to older manually entered patients that never match a synced record.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>The owner asked that DenialDesk sync patients rather than hold them; manual entry is kept only for practices without a connection.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>Yes/no on retiring manual registration, plus the rule for unmatched manual patients (stay read-only, archive, or editable).</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-046)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>Before PI3</t>
         </is>
       </c>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>OA-047</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Confirm that patient phone and email are not synced from the EHR (billing minimum only).</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>Minimum necessary (R-5.1.2): the 837P doesn't need them.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Confirm, or name which contact fields billing staff need and why.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-047); R-5.1.2</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>Before PI2 merge</t>
         </is>
       </c>
-      <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
+      <c r="K47" s="3" t="n"/>
+      <c r="L47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>OA-048</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Decide what happens to synced patients when a practice disconnects or switches EHRs: stay read-only, convert back to manual, or link to the new connection. Also: after a connection is revoked, synced patients stay read-only and no longer update — how is an amendment request honored for them (45 CFR 164.504(e)(2)(ii)(F); counsel)?</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>Offboarding and EHR migrations need a defined path; nothing is ever deleted (R-9.2.1).</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>Chosen rule.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-048); R-9.2.1</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="n"/>
+      <c r="K48" s="3" t="n"/>
+      <c r="L48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>OA-049</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Vendor/Account</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Register DenialDesk as a backend-services app in vendor FHIR sandboxes (Epic on FHIR, Oracle Health, athenahealth) and decide whether to allow-list them in pre-production.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Pre-production uses only the built-in synthetic sandbox today; vendor sandboxes (synthetic data) test real EHR behavior.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Which vendors, the sandbox accounts set up by the owner (no secrets in this sheet), and a yes/no on allow-listing them in pre-production.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-049); ADR 0003</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>Before PI4</t>
         </is>
       </c>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
+      <c r="K49" s="3" t="n"/>
+      <c r="L49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>OA-050</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Approve building FHIR Bulk Data export (PI4) before the first real practice is connected.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>US Core does not require the population-wide search PI2 uses; certified EHRs offer Bulk Data for population access.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>Yes/no and target date.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-050)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K50" s="2" t="n"/>
-      <c r="L50" s="2" t="n"/>
+      <c r="K50" s="3" t="n"/>
+      <c r="L50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>OA-051</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Decide who confirms at onboarding that the practice's EHR app registration only exposes that practice's own patients.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>Minimum necessary (R-5.1.2): a registration scoped to a whole health system would over-collect.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Named role (practice admin, DenialDesk onboarding, or both) and the onboarding checklist step.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-051); R-5.1.2</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K51" s="2" t="n"/>
-      <c r="L51" s="2" t="n"/>
+      <c r="K51" s="3" t="n"/>
+      <c r="L51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>OA-052</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Decide how to handle patients the EHR labels restricted or very restricted (R/V) until sensitivity masking (patients P4) ships: import them showing 'Restricted in source', or hold them back from sync.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>Threat model I3 is blocking before real data.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>Chosen rule.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-052); R-3.5.1</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K52" s="2" t="n"/>
-      <c r="L52" s="2" t="n"/>
+      <c r="K52" s="3" t="n"/>
+      <c r="L52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>OA-053</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Decide whether MRN conflicts (same MRN, different birth date) are fixed in the EHR only, or need an admin tool in DenialDesk.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>Conflicts are reported and skipped; a practice needs a way to clear them.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Chosen approach.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-053)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>Before PI3</t>
         </is>
       </c>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
+      <c r="K53" s="3" t="n"/>
+      <c r="L53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>OA-054</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Clarification</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Assign a requirement ID for EHR/PM interoperability (REQUIREMENTS §8.8 has no numbered item for it).</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>Every change must map to a requirement ID (CLAUDE.md).</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>Approve a new ID (e.g. R-8.8.1) and its wording.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-054); REQUIREMENTS §8.8</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>Before PI1 merge</t>
         </is>
       </c>
-      <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="n"/>
+      <c r="K54" s="3" t="n"/>
+      <c r="L54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>OA-055</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Confirm that dependents (policy subscriber is not the patient) get no synced coverage until patients P2 adds subscriber details.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>Their claims can't be billed from synced data until then.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>Accept, or reprioritize patients P2.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-055)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>Before PI2 merge</t>
         </is>
       </c>
-      <c r="K55" s="2" t="n"/>
-      <c r="L55" s="2" t="n"/>
+      <c r="K55" s="3" t="n"/>
+      <c r="L55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>OA-056</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Confirm a 15-minute scheduled patient sync interval.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>Balances freshness against EHR API rate limits.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>Interval (or 'on demand only').</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-056)</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-27</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>Before PI3</t>
         </is>
       </c>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
+      <c r="K56" s="3" t="n"/>
+      <c r="L56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>OA-057</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Confirm the safeguard against one practice pulling another practice's EHR patients: the platform operator approves every real EHR connection after checking its address and client ID with the practice's EHR administrator, the same EHR registration can't be used by two practices, and each connection gets its own signing key where the EHR vendor supports it.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>Security review 2026-09-28 (Critical C1): with one shared DenialDesk signing key, a practice admin could enter another practice's EHR address and client ID and sync its patients.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Accept the three safeguards, or choose differently (e.g. per-practice keys only).</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (OA-057); R-7.2.4</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>patient-integrations session 2026-09-28</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>Before PI1b</t>
         </is>
       </c>
-      <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="n"/>
+      <c r="K57" s="3" t="n"/>
+      <c r="L57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>OA-058</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Confirm that practice-wide denial totals without identifiers (counts and sums on the home page) are not a PHI read and need no audit event.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>The home page revamp shows live open-denial totals without auditing each view; Insight reports audit aggregates as PHI-adjacent, so the rule should be set once.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>Yes/no; if no, the agent adds an audit event to the home page strip.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>R-7.5.1; specs/welcome-page.md</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>home-page revamp session 2026-09-27</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>Before the Azure (production) launch</t>
         </is>
       </c>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
+      <c r="K58" s="3" t="n"/>
+      <c r="L58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>OA-059</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Confirm three settings for payer custom fields: (1) who may edit a payer's custom field values -- today admin+manager (canEditPayerFields), narrower than the claim/patient roles which also include specialists; (2) that a specialist may still open ('reveal') a locked payer value they cannot edit, since reveal uses the same single reveal-role rule as every other record type (canWorkDenials, ADR 0007) rather than canEditPayerFields; (3) whether payer custom field values are Confidential business data or PHI, since free text on a payer field could still hold patient details, and whether the six patient-oriented sensitivity categories (HIV, mental health, SUD, genetic, minor, reproductive health) are the right lock for a payer field at all, or whether a generic 'confidential' category should be added.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>Payers are practice configuration, not a patient record, but their custom fields are free text an administrator could still use to record something patient-specific; the current role split and sensitivity categories are the implementing agent's best guess (R-5.1.2 minimum necessary), not an owner decision.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>A yes/confirm on the current role split (or a different role list), confirmation of the data classification, and a decision on whether to add a payer-appropriate sensitivity category.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>specs/settings-and-custom-fields.md; R-5.1.2</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>custom-fields PR 4 session 2026-09-28</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>Before first real practice</t>
         </is>
       </c>
-      <c r="K59" s="2" t="n"/>
-      <c r="L59" s="2" t="n"/>
+      <c r="K59" s="3" t="n"/>
+      <c r="L59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>OA-060</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Confirm that patient names read only to order the unsubmitted claims queue by patient (never shown or returned beyond the displayed page) are covered by the claim.list_viewed audit event and need no separate audit event.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>Settles whether sort-only PHI reads need their own audit trail (R-7.5.1) or only minimum-necessary handling (R-5.1.2).</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>Yes (covered) / No (add an audit event for sort-only reads).</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H60" s="3" t="inlineStr">
         <is>
           <t>R-7.5.1, R-5.1.2; specs/record-pages.md P4</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>compliance-checker 2026-09-28</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>Before launch</t>
         </is>
       </c>
-      <c r="K60" s="2" t="n"/>
-      <c r="L60" s="2" t="n"/>
+      <c r="K60" s="3" t="n"/>
+      <c r="L60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>OA-061</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>Confirm you accept that the free-text EHR/PM connection name is shown to every role on every signed-in page (the Patients data-source drop-down), guarded only by a 'no patient information' hint and length/invisible-character checks — or ask for a stronger guard (e.g. refuse names that look like MRNs or person names).</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>The name now appears in the header of every page, including screen shares and screenshots; only the owner can accept the residual risk.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>Accept as is / require a stronger guard (which).</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>R-7.4.8, R-5.1.2; specs/patient-integrations.md PI1b; specs/erp-shell.md</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>compliance-checker 2026-09-28</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>Before first real practice</t>
         </is>
       </c>
-      <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="n"/>
+      <c r="K61" s="3" t="n"/>
+      <c r="L61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>OA-062</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Decide whether the FHIR transport should require TLS 1.3 as a minimum.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>R-7.3.1 requires TLS 1.2+ and prefers 1.3. The transport allows 1.2 (ECDHE + AEAD suites only) and negotiates 1.3 when offered. Requiring 1.3 is stronger but would lock out EHR vendors that only support 1.2.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>Keep TLS 1.2 minimum (current), or require 1.3 (and, if so, which vendors are known to be 1.2-only).</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H62" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md PI2a; R-7.3.1</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-28</t>
         </is>
       </c>
-      <c r="J62" s="2" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>Before the first real practice</t>
         </is>
       </c>
-      <c r="K62" s="2" t="n"/>
-      <c r="L62" s="2" t="n"/>
+      <c r="K62" s="3" t="n"/>
+      <c r="L62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>OA-063</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Confirm the step-up MFA choices built in PI2a (cross-ref OA-045): (a) the step-up window is 5 minutes, and a fresh sign-in TOTP counts as a step-up; (b) a successful step-up rotates the session token and cookie; (c) step-up attempts share the sign-in lockout counter, a failed one never resets it, and a successful one keeps earlier failures and gives back only its own attempt (so successful step-ups can't add up to a lockout), and the attempt that would reach the lockout limit is refused before its code is checked and is what locks the account for the usual 15 minutes, audited as auth.locked_out (so a correct code never causes the lock, and the lock expires on its own; an attempt while already locked is audited as auth.step_up_refused); (d) step-up is required to Resume a paused or errored connection (and, once built, Submit and payer mapping) but NOT to Pause or Revoke, because those are the safe direction and the emergency stop for a suspected compromise; (e) TOTP is the only step-up factor for now: a known gap against R-7.2.2's phishing-resistant MFA (WebAuthn), to close before the first real (non-sandbox) EHR connection goes live.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>Step-up is the control that stops a hijacked or unattended admin session from restarting patient sync; these are owner-confirmable defaults rather than agent judgment calls, and (e) is a recorded gap against a named requirement that needs a human decision on timing.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>Confirm (a)-(d) as built or say what to change; decide whether WebAuthn (or another phishing-resistant factor) must ship before the first real EHR connection, or whether TOTP is accepted until then.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md PI2a; R-7.2.2; cross-ref OA-045</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>patient-integrations PI2a lifecycle session 2026-09-28</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>Before first real (non-sandbox) EHR connection</t>
         </is>
       </c>
-      <c r="K63" s="2" t="n"/>
-      <c r="L63" s="2" t="n"/>
+      <c r="K63" s="3" t="n"/>
+      <c r="L63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>OA-064</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Vendor/Account</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Generate a pre-production ES384 signing key and set it as INTEGRATION_SIGNING_KEY, a functions-only secret, in the Netlify site settings.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>Test connection and the token request sign with this shared key, and its public half is published at /.well-known/jwks.json for a vendor sandbox administrator to register. Without it, Test connection reports that the signing key isn't configured. Never use it in production (production refuses it) and never commit it.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>Confirmation that the secret is set for the Netlify functions only (not the build or the client), and the JWKS URL once it serves a key. Generate with: openssl ecparam -name secp384r1 -genkey -noout | openssl pkcs8 -topk8 -nocrypt (PKCS#8 PEM). Register this key only with vendor sandbox tenants holding synthetic data, never with a live practice EHR. Never use it in production (production refuses it).</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md PI2a Keys; R-7.3.4, R-7.3.5</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>agent 2026-09-28</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>Before testing against a vendor sandbox</t>
         </is>
       </c>
-      <c r="K64" s="2" t="n"/>
-      <c r="L64" s="2" t="n"/>
+      <c r="K64" s="3" t="n"/>
+      <c r="L64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>OA-065</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Confirm three PI2a coordinator decisions: (a) Submit's Test-connection gate is stricter than the spec's plain wording — the newest test for the connection must be a pass within 24 h, bound to the tested base URL, client ID, token endpoint and key, issuer, and signing kid (a later failed test or transport refusal voids it); (b) pre-production signs every connection with one shared key (INTEGRATION_SIGNING_KEY), accepted as a pre-production exception with the operator verifying client_id ownership outside the app at approval. (c) A refused Submit says "This endpoint and client ID are already connected": it reveals that some practice holds that endpoint and client ID pair, with no identity disclosed. It is bounded by the Test connection limits (5 per connection and 20 per practice per 10 minutes) and the Submit limit (10 per practice per 10 minutes), and audited. Accept this signal, or reject it and refuse with the generic 'could not be submitted' wording.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>(a) decides when a practice may submit a connection; (b) is a residual risk recorded in the threat model (S3): an admin who knows another practice's client_id at the same EHR could get a passing test for it. Synthetic data only; per-connection Key Vault keys remove it in production.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>Confirm (a) and (b) as built, or say what to change (e.g. 'any pass in 24 h counts'). (c) Accept or reject the registry-conflict signal.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI2a Test connection, Keys; PI1c Approve); docs/threat-models/patient-integrations.md S3; R-7.3.4, R-7.3.5</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>Coordinator (PR #87 compliance review), 2026-09-28</t>
         </is>
       </c>
-      <c r="J65" s="2" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>Before the first real connection</t>
         </is>
       </c>
-      <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="n"/>
+      <c r="K65" s="3" t="n"/>
+      <c r="L65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>OA-066</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Approve the lists behind Approve's verification record. Verification method: phone call-back to a number on file, video call with the EHR/PM administrator, written confirmation from the administrator's verified address, confirmed in the EHR/PM vendor's app registry. Contact's role at the practice: EHR/PM administrator, practice administrator, practice IT contact, vendor representative, other.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>The spec asks for a "method code" and "the contact's role" but lists neither; the builder proposed these. They are the evidence that the operator verified the connection with the practice out of band, so they should match what onboarding will really do. (OA-051 is a different question: who confirms the population scope.)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>Confirm the lists, or give the changes (add, remove, rename).</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI1c); src/domain/integrations/approval-codes.ts</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K66" s="2" t="n"/>
-      <c r="L66" s="2" t="n"/>
+      <c r="K66" s="3" t="n"/>
+      <c r="L66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>OA-067</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>R-15.9 sign-off for the operator alert on integration.registry_conflict: allow either (1) a SECURITY DEFINER function integration_registry_conflict_record(connection_id) that Submit calls to write an operator-only record of the HOLDING connection's ID, or (2) an INSERT-only grant on a new operator-only table to the app role.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>A refused Submit reveals only that some practice holds the endpoint and client ID pair. The operator needs to know who holds it to follow up a squatting or confused-deputy attempt (threat model S2), but the practice's own audit event can't show it, and the record must live outside the tenant's audit log and never reach the customer audit viewer. Writing it from a practice session is a privilege change, so it needs your sign-off; no migration is written until you decide.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>Choose (1) or (2), or reject the alert and say what the operator should rely on instead.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>docs/threat-models/patient-integrations.md S2; docs/specs/patient-integrations.md (PI1c); R-15.9</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K67" s="2" t="n"/>
-      <c r="L67" s="2" t="n"/>
+      <c r="K67" s="3" t="n"/>
+      <c r="L67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>OA-068</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Confirm that Reject should clear the practice's U.S.-residency attestation and the discovered token endpoint/issuer, as Withdraw does (built that way), rather than leave them on the returned draft.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>The spec says only that Reject returns the connection to draft and releases the registry claim. The endpoint becomes editable again, so a different endpoint must be attested and discovered afresh; migration 0042 refuses a stale attestation on the next Submit either way.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>Confirm as built, or say to leave them.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI1c); docs/specs/patient-integrations.md (Withdraw)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K68" s="2" t="n"/>
-      <c r="L68" s="2" t="n"/>
+      <c r="K68" s="3" t="n"/>
+      <c r="L68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>OA-069</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Write the Notifications spec that the activation notice depends on: who is notified when a connection is approved (all practice administrators), the notice wording, how long notices are kept, and whether a PHI-free e-mail may be sent.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>The spec requires every practice administrator to be notified on activation (and, wanted, on revoke, SOC 2 CC7.3). The app has no in-app notice mechanism, so nothing is sent today; the practice only sees the new status on its pages. Building a notices system is its own feature.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>Who is notified, retention, and yes/no on PHI-free e-mail; then a builder slice can build the notice.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI1c); specs/settings-and-custom-fields.md S3</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K69" s="2" t="n"/>
-      <c r="L69" s="2" t="n"/>
+      <c r="K69" s="3" t="n"/>
+      <c r="L69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>OA-070</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Decide how long approval evidence is kept: operator.integration_approved and operator.integration_rejected audit events kept for the life of the connection plus 6 years and under legal hold, or add dedicated approval columns (date verified, contact role, ownership confirmed) later.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>The date, the contact's role, and the client-ID ownership confirmation are recorded only in the audit event; the connection row has no columns for them. They are the proof that a real connection was verified with the practice before PHI flowed (HIPAA documentation retention, 45 CFR 164.316(b)(2), six years).</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>Retention rule (with counsel if needed), and whether to add columns.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H70" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI1c); R-7.5.1; 45 CFR 164.316(b)(2)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K70" s="2" t="n"/>
-      <c r="L70" s="2" t="n"/>
+      <c r="K70" s="3" t="n"/>
+      <c r="L70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>OA-071</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Build an operator-side revoke of a live connection before the first real connection, and say who may use it.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>The lifecycle allows revoke by "admin or operator", but only a practice administrator can revoke today. In a suspected compromise, or when the practice's administrator is unreachable, the platform operator has no way to stop a live sync.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>Yes/no and the conditions; then a spec item (added, unticked) is built.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI1c); docs/runbooks/integration-offboarding.md</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="J71" s="3" t="inlineStr">
         <is>
           <t>Before first real connection</t>
         </is>
       </c>
-      <c r="K71" s="2" t="n"/>
-      <c r="L71" s="2" t="n"/>
+      <c r="K71" s="3" t="n"/>
+      <c r="L71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>OA-072</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Accept that operator approval is a single-person control, and confirm that exactly one named person uses the platform operator account. Otherwise plan per-person operator accounts before production.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>Approve depends on one account's judgment and one person's out-of-band verification. HIPAA unique user identification (45 CFR 164.312(a)(2)(i)) needs each action attributable to one person; a shared operator account would not be. The audit event records the account and its session, not a person.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>Accept single-person approval (yes/no), and confirm who holds the account; or a plan for per-person operator accounts and a second approver.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H72" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI1c); docs/specs/operator-login.md; 45 CFR 164.312(a)(2)(i)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>Before production</t>
         </is>
       </c>
-      <c r="K72" s="2" t="n"/>
-      <c r="L72" s="2" t="n"/>
+      <c r="K72" s="3" t="n"/>
+      <c r="L72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>OA-073</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Decide whether Approve must be gated by an operator-realm step-up (fresh second-factor check within a short window), and by when. Reject would stay ungated.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>Practice-side Submit and Resume need a step-up within 5 minutes; the operator's Approve, the control that lets a real connection go live, has none beyond the sign-in session (security review M1). It is not built; recorded as an unticked spec item.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>Yes/no and the deadline (proposed: before the Azure cutover and the first real connection); the audit will then record step_up_verified_at.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI1c); R-7.2.2; cross-ref OA-063</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>PI1c approval session + compliance/security review of PR #89, 2026-09-28</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>Before Azure cutover</t>
         </is>
       </c>
-      <c r="K73" s="2" t="n"/>
-      <c r="L73" s="2" t="n"/>
+      <c r="K73" s="3" t="n"/>
+      <c r="L73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>OA-074</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>Decide whether CI (and local development) runs the integration suite as a non-superuser, NOBYPASSRLS schema-owner role, so FORCE ROW LEVEL SECURITY is exercised on the owner and platform paths.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>CI connects to PostgreSQL as a superuser, which ignores row-level security even on FORCE tables, so tests never exercise the owner path (`withTenantAsPlatform`: operator Approve and Reject, BAAs, University access) or owner-role reads under the tenant policy. A missing `app.tenant_id` or a policy that hides rows from the owner would pass CI and surface at the first non-superuser deploy (Netlify preview, Azure). Changing the CI database role is a privilege change, so it needs the owner's sign-off (R-15.9).</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>Yes/no and the timing. Proposal: migrate and run `pnpm test:integration` as a non-superuser, NOBYPASSRLS owner role (setup that must bypass policies keeps a separate superuser connection), plus a test that the connection role has neither rolsuper nor rolbypassrls. Then a CI and docker-compose change is built.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (Test infrastructure gap); docs/PROJECT_STATE.md; R-15.9; R-7.2.4</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>PI2b UI slice, after PR #89 and PR #91 reviews, 2026-09-28</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>Before the Azure cutover</t>
         </is>
       </c>
-      <c r="K74" s="2" t="n"/>
-      <c r="L74" s="2" t="n"/>
+      <c r="K74" s="3" t="n"/>
+      <c r="L74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>OA-075</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Say whether a payor key (`Organization/&lt;id&gt;`, an insurer reference reported by the EHR/PM) is detached from any patient's PHI, or is PHI where it sits on a patient row.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>The key names an insurer, not a person, but it is stored on each synced patient row (`coverage_payor_key`, classified Restricted PHI) and repeated in `integration_payer_mappings` (classified Confidential configuration). The answer decides whether the mapping table is reclassified from Confidential to Restricted (access, audit, retention, and log handling follow the class). Until answered, the payer mapping page is audited and no audit event or log carries a key.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>Detached (keep Confidential) or not detached (reclassify to Restricted), with the reasoning counsel or the compliance owner accepts.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (Classification, PI2b); REQUIREMENTS §9.1</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>PI2b UI slice, compliance review of PR #91, 2026-09-28</t>
         </is>
       </c>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>Before the first real connection</t>
         </is>
       </c>
-      <c r="K75" s="2" t="n"/>
-      <c r="L75" s="2" t="n"/>
+      <c r="K75" s="3" t="n"/>
+      <c r="L75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>OA-076</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Sign off (R-15.9) on migration 0043 before it runs anywhere beyond a local or test database: it seeds one identity, the integration service-principal `users` row (id d3a7c0de-5a1c-4e11-8a0c-0000000d0d01, disabled, unusable password hash, no membership, no session, no second factor) that the sync engine writes as. It adds no GRANT, REVOKE, role, SECURITY DEFINER function, or RLS policy change.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>The sync engine's audit events and its `updated_by` on connection and payer-mapping rows need a user row (foreign keys). A seeded account is an identity change under R-15.9 even though it cannot sign in. The same migration also changes two trigger functions (stamp `updated_at` with the real clock on status changes; abandon queued and running runs on pause and error) and replaces the sandbox CHECK constraint (the issuer is the base URL), none of which changes a privilege.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>Approve, or ask for a different shape (for example an account outside `users`, which would mean dropping the foreign keys the engine writes under). Recorded on the PR.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI2b); drizzle/0043_patient_integrations_sync_engine.sql; R-15.9</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>PI2b sync engine builder, 2026-09-29</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>Done 2026-09-29 (was: before 0043 runs beyond local and test databases; Netlify previews already applied it)</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K76" s="3" t="inlineStr">
         <is>
           <t>APPROVED by the owner 2026-09-29 (R-15.9): the integration service-principal seed in migration 0043 (disabled `users` row, unusable password hash, no membership, no session, no second factor). No GRANT, REVOKE, role, SECURITY DEFINER or RLS change. Follow-up, not a change to 0043: a later migration should use ON CONFLICT (id) DO NOTHING (PR #98 review L3). Approval evidence: https://github.com/jselvalugo/DenialDesk/pull/98#issuecomment-5881787399</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>OA-077</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Decide three small things about the sync engine: (a) whether "Sync now" may keep running the whole sync inside the request until background jobs ship (the sandbox takes seconds; a large practice would not fit a serverless time limit); (b) whether a newly synced patient under 18 should get the neutral history note `review_required` (no tag is suggested or set, and no code names minors); (c) whether Coverage-only changes should be searched with `Coverage?_lastUpdated` (built later) or left to the weekly reconciliation in PI3.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>(a) A run that the platform kills leaves its committed pages and is retried from the old watermark after the 20-minute lease; (b) rationale for a neutral note: the sync-history page is not audited and must hold no PHI, so a code that said "minor" (or named any sensitivity category) would disclose a category of patient outside the audited channels; `review_required` only says a person should look, and the audited patient page is where the reason can be seen (whether minors should also be restricted by default is OA-081); (c) until then a Coverage-only change reaches a patient only when the Patient changes or a payer mapping is saved.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>A yes/no on (a) and (b), and A or B on (c).</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI2b, "Sync run and issue codes"); OA-056</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>PI2b sync engine builder, 2026-09-29</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>Before the first real connection</t>
         </is>
       </c>
-      <c r="K77" s="2" t="n"/>
-      <c r="L77" s="2" t="n"/>
+      <c r="K77" s="3" t="n"/>
+      <c r="L77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>OA-078</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Approve an ADR and a re-encryption migration to bind field-level encryption to its record: today the encrypted member ID (and every other encrypted field) has no additional authenticated data (AAD) tying the ciphertext to its row and practice. Proposed design: ADR 0011 (docs/decisions/0011-field-encryption-aad-envelope-v2.md, PR #97) with spec docs/specs/field-encryption-aad.md; also answer spec questions 2-5 and 12: run the re-encryption job on pre-production or wipe and re-seed (security review recommends re-seed); who confirms the legacy cut-off; confirm Azure production starts empty; whether the pre-production FIELD_ENCRYPTION_KEY was ever changed; whether production refuses legacy (v1) provider TINs.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>AES-GCM without AAD lets a ciphertext be copied from one row or practice to another and still decrypt. Row-level security and the application's own checks prevent that today, but a database-level mistake or a compromised app role would not be caught by the cipher. Applies app-wide (SSN, MBI, member IDs, bank data), not only to synced patients; the fix needs a format change and re-encrypting every stored value.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>Approval of ADR 0011 (or requested changes) and the timing; answers to spec questions 2-5 and 12.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI2b); src/lib/crypto/field.ts; CLAUDE.md non-negotiable 6; R-7.3.3; SC-B7.1; ADR 0011; docs/specs/field-encryption-aad.md</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
         <is>
           <t>PR #98 review (security M3), 2026-09-29</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>Before the first real practice</t>
         </is>
       </c>
-      <c r="K78" s="2" t="n"/>
-      <c r="L78" s="2" t="n"/>
+      <c r="K78" s="3" t="n"/>
+      <c r="L78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>OA-079</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Confirm that linking a synced patient overwrites a manually entered patient with the same MRN and birth date, including the name, address and member ID the practice typed (and clears the member ID when the EHR coverage is not usable).</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>The spec says an exact MRN and birth-date match links the two; the sync then owns those fields and the practice can no longer edit them. It is the one path by which the EHR can replace practice-entered data, with no human confirmation.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>Confirm as built, or ask for a confirmation step (for example an administrator reviews each proposed link) or for keeping the manual member ID when the EHR has none.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (PI2b upsert and linking); threat model T3, T5</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
         <is>
           <t>PR #98 review (L5), 2026-09-29</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>Before the first real connection</t>
         </is>
       </c>
-      <c r="K79" s="2" t="n"/>
-      <c r="L79" s="2" t="n"/>
+      <c r="K79" s="3" t="n"/>
+      <c r="L79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>OA-080</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>Decide whether to store the source's sensitivity category (for example HIV, psychiatric, substance use) or only the `source_restricted` flag.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>Today the sync stores the recognized labels in a fixed vocabulary on the patient row (`source_sensitivity`) as well as the flag. A category on a patient row is itself sensitive; the flag alone is enough to restrict, and the category is only needed if masking must differ by category (for example a 42 CFR Part 2 program).</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>Keep category and flag, or flag only (and drop `source_sensitivity` in a later migration).</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (field mapping); threat model I4; OA-052</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="I80" s="3" t="inlineStr">
         <is>
           <t>PR #98 review (N1), 2026-09-29</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="J80" s="3" t="inlineStr">
         <is>
           <t>Before patients P4 masking</t>
         </is>
       </c>
-      <c r="K80" s="2" t="n"/>
-      <c r="L80" s="2" t="n"/>
+      <c r="K80" s="3" t="n"/>
+      <c r="L80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>OA-081</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>Decide whether patients under 18 should be restricted by default (masked like a restricted-in-source patient).</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>The sync records only the neutral note `review_required` for a new minor and sets no tag or restriction (a code that named a minor would disclose a category on an unaudited page). Whether minors are treated as sensitive at all is a policy and legal question (Florida minor-consent rules), not a technical one.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>Yes (restrict by default), no, or restrict only for services with minor-consent rules, with counsel's reasoning.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H81" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md (field mapping, birth_date); threat model I4; OA-077(b)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="I81" s="3" t="inlineStr">
         <is>
           <t>PR #98 review (N2), 2026-09-29</t>
         </is>
       </c>
-      <c r="J81" s="2" t="inlineStr">
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>Before patients P4 masking</t>
         </is>
       </c>
-      <c r="K81" s="2" t="n"/>
-      <c r="L81" s="2" t="n"/>
+      <c r="K81" s="3" t="n"/>
+      <c r="L81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>OA-082</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Legal/Compliance</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>Accept, or refuse, that restricted-in-source patients are visible to every role in the practice until patients P4 masking ships.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>The sync marks patients restricted (`source_restricted`) but nothing masks them yet, so any staff member who can see the Patient Register sees them. The interim is safe only with synthetic data (pre-production); real data must wait for masking (threat model I4, blocking before real data). With the sync also refusing real connections until PI4, the interim exposes no real patient today.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>Accept the interim for synthetic data only (yes/no), and confirm masking stays a blocker for the first real connection.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>docs/specs/patient-integrations.md; threat model I4; R-3.5.1, R-4.5.1; OA-052</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I82" s="3" t="inlineStr">
         <is>
           <t>PR #98 review (N3), 2026-09-29</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>Before the first real connection</t>
         </is>
       </c>
-      <c r="K82" s="2" t="n"/>
-      <c r="L82" s="2" t="n"/>
+      <c r="K82" s="3" t="n"/>
+      <c r="L82" s="3" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -4951,8 +4951,8 @@
           <t>Before the first real practice</t>
         </is>
       </c>
-      <c r="K83" s="3" t="inlineStr"/>
-      <c r="L83" s="3" t="inlineStr"/>
+      <c r="K83" s="3" t="n"/>
+      <c r="L83" s="3" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -5005,8 +5005,8 @@
           <t>Before the first real practice</t>
         </is>
       </c>
-      <c r="K84" s="3" t="inlineStr"/>
-      <c r="L84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="n"/>
+      <c r="L84" s="3" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -5443,7 +5443,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>OA-097</t>
+          <t>OA-093</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -5458,46 +5458,46 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Decision</t>
+          <t>Clarification</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Decide whether changing a provider's billing name or address (not only the TIN) should also require a fresh step-up MFA on Settings &gt; Billing.</t>
+          <t>Decide whether Spanish and Portuguese payer-facing appeal letter templates are needed, and whether template edits need their own version history.</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>They go on every claim, so a wrong address misdirects payment. C3a-S asks for the step-up only when the TIN is set or changed, to keep the page usable.</t>
+          <t>A letter goes to the payer, so A2 ships English templates only (the UI around them is en/es/pt). A template history table would need a new GRANT (R-15.9).</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>Yes or no, and if yes which fields.</t>
+          <t>Yes/no per language; yes/no for template history.</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>specs/claims.md C3a-S; R-7.2.2, HC-4.2</t>
+          <t>specs/appeals.md A2; R-7.11.2</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>agent Claude C3a-S (vigilant-tesla-ps41e9), 2026-09-29</t>
+          <t>agent Claude A2 (vigilant-tesla-ps41e9), 2026-09-29</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>Before launch</t>
-        </is>
-      </c>
-      <c r="K93" s="3" t="n"/>
-      <c r="L93" s="3" t="n"/>
+          <t>Before A3</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr"/>
+      <c r="L93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>OA-101</t>
+          <t>OA-094</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -5507,51 +5507,51 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Legal/Compliance</t>
+          <t>Decision</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Decide whether local development may keep Next.js's unavoidable 'next dev' update check (it asks registry.npmjs.org for newer Next.js versions; no opt-out in 16.3.6) under a written, time-boxed exception ADR signed by the Security and Privacy Officers (HC §0), or keep SC-A2.6 tracked as a known gap.</t>
+          <t>Decide whether an exported appeal letter may show the full member ID (decrypted at print time, audited) or only the last four characters.</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>SC-A2.6 bans update checks; everything else that phones home is now off. No PHI is involved (local development holds synthetic data only).</t>
+          <t>Payers often need the full ID. A2 masks it (minimum necessary, HC-3.3; field-level encryption, R-7.3.3) and the full ID is not available in letters yet.</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Accept (officers sign an exception ADR the agent drafts) or keep tracked.</t>
+          <t>Keep masked, or allow the full ID on the print view only.</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>SC-A2.6; HC §0; PR #96</t>
+          <t>specs/appeals.md A2; HC-3.3; R-7.3.3</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>SC gap PRs session 2026-09-29</t>
+          <t>agent Claude A2 (vigilant-tesla-ps41e9), 2026-09-29</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>Before the first real practice</t>
-        </is>
-      </c>
-      <c r="K94" s="3" t="n"/>
-      <c r="L94" s="3" t="n"/>
+          <t>Before real data</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr"/>
+      <c r="L94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>OA-102</t>
+          <t>OA-095</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -5571,41 +5571,41 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>Approve a separate RATE_LIMIT_HASH_KEY so src/lib/rate-limit.ts stops reusing FIELD_ENCRYPTION_KEY as a hash salt (spec question 6).</t>
+          <t>Decide where a payer's appeals mailing address and fax number should live so letters can merge them (a new column on payers, or a per-appeal field).</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>One key per purpose; rotating the field key must not reset rate-limit windows.</t>
+          <t>The payers table has no address column, so starter letters carry a fill-in placeholder for it. A new column needs a migration.</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Yes/no; if yes the agent adds the variable in a follow-up PR (never the value in the sheet).</t>
+          <t>Choice of location and where the addresses come from.</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1; R-7.3.4; docs/specs/field-encryption-aad.md</t>
+          <t>specs/appeals.md A2; specs/payer-catalog.md</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+          <t>agent Claude A2 (vigilant-tesla-ps41e9), 2026-09-29</t>
         </is>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>Before the first key rotation</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="n"/>
-      <c r="L95" s="3" t="n"/>
+          <t>Before A3</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>OA-103</t>
+          <t>OA-096</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -5625,41 +5625,41 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>Decide the ADR 0011 follow-ups (spec questions 7-10): keep retired keys decrypt-only for append-only custom-field history and synced patients or approve a re-encryption path (R-15.9); key retirement: backup and point-in-time retention periods, no key destruction until legal hold exists, and Security plus Privacy Officer sign-off to destroy a key; run one pre-production key-rotation drill after the cut-off; whether an 835 or find-by-member-ID feature gets a tenant-keyed blind index.</t>
+          <t>Confirm who may attest and export appeal letters (built: admin, manager, specialist; compliance read-only), whether a second person must review a letter the author wrote, and whether recording a submission should require an attestation.</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Shapes the Azure-cutover key rotation ADR and any member-ID matching feature.</t>
+          <t>R-7.11.2 requires a named user to approve before anything reaches a payer. A2 blocks export without an attestation but does not require four eyes or gate 'record submission'.</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>An answer to each of the four (rotation path, key retirement policy, drill, blind index); the rotation parts can wait for the cutover ADR.</t>
+          <t>A decision on each of the three.</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1; R-7.3.4; R-15.9; docs/specs/field-encryption-aad.md</t>
+          <t>specs/appeals.md A2; R-7.11.2, R-5.1.2</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+          <t>agent Claude A2 (vigilant-tesla-ps41e9), 2026-09-29</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>Azure cutover</t>
-        </is>
-      </c>
-      <c r="K96" s="3" t="n"/>
-      <c r="L96" s="3" t="n"/>
+          <t>Before A3</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr"/>
+      <c r="L96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>OA-104</t>
+          <t>OA-097</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -5679,39 +5679,309 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>Decide whether rcm_claim_lines.account_number (the practice's patient account number in revenue-cycle files) is field-encrypted like member IDs.</t>
+          <t>Decide whether changing a provider's billing name or address (not only the TIN) should also require a fresh step-up MFA on Settings &gt; Billing.</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>HC-7.3/R-7.3.3 list only SSN, MBI, member IDs, and bank data, so plaintext breaks no MUST rule today; it is still an HC-1.1 identifier protected only by at-rest encryption and RLS.</t>
+          <t>They go on every claim, so a wrong address misdirects payment. C3a-S asks for the step-up only when the TIN is set or changed, to keep the page usable.</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Yes/no from the Security and Privacy Officers; if yes, the agent adds it to the ADR 0011 build.</t>
+          <t>Yes or no, and if yes which fields.</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1; HC-1.1; HC-7.3; ADR 0011; docs/specs/field-encryption-aad.md</t>
+          <t>specs/claims.md C3a-S; R-7.2.2, HC-4.2</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>SC-B7.1 AAD plan session 2026-09-29</t>
+          <t>agent Claude C3a-S (vigilant-tesla-ps41e9), 2026-09-29</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>Before the first real practice</t>
+          <t>Before launch</t>
         </is>
       </c>
       <c r="K97" s="3" t="n"/>
       <c r="L97" s="3" t="n"/>
     </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>OA-098</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Give R-15.9 sign-off on the three table GRANTs in drizzle/0047_appeal_letters.sql, listed verbatim: GRANT SELECT, INSERT, UPDATE ON "appeal_letter_templates" TO denialdesk_app; GRANT SELECT, INSERT ON "appeal_letter_versions" TO denialdesk_app; GRANT SELECT, INSERT ON "appeal_letter_attestations" TO denialdesk_app; (the same migration also adds append-only triggers and replaces purge_demo_practices(), which is not SECURITY DEFINER).</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>SECURE_CODING SC-B5.3 and R-15.9 require human sign-off on any GRANT. These follow the existing pattern (table grants in the creating migration, no role, no SECURITY DEFINER); the two history tables get no UPDATE or DELETE.</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Approve or decline each of the three lines.</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>specs/appeals.md A2; SC-B5.3; R-15.9</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>agent Claude A2 (vigilant-tesla-ps41e9), 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>Before the A2 PR merges</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>OA-101</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether local development may keep Next.js's unavoidable 'next dev' update check (it asks registry.npmjs.org for newer Next.js versions; no opt-out in 16.3.6) under a written, time-boxed exception ADR signed by the Security and Privacy Officers (HC §0), or keep SC-A2.6 tracked as a known gap.</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>SC-A2.6 bans update checks; everything else that phones home is now off. No PHI is involved (local development holds synthetic data only).</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>Accept (officers sign an exception ADR the agent drafts) or keep tracked.</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>SC-A2.6; HC §0; PR #96</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>SC gap PRs session 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="n"/>
+      <c r="L99" s="3" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>OA-102</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Approve a separate RATE_LIMIT_HASH_KEY so src/lib/rate-limit.ts stops reusing FIELD_ENCRYPTION_KEY as a hash salt (spec question 6).</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>One key per purpose; rotating the field key must not reset rate-limit windows.</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no; if yes the agent adds the variable in a follow-up PR (never the value in the sheet).</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1; R-7.3.4; docs/specs/field-encryption-aad.md</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>Before the first key rotation</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="n"/>
+      <c r="L100" s="3" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>OA-103</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Decide the ADR 0011 follow-ups (spec questions 7-10): keep retired keys decrypt-only for append-only custom-field history and synced patients or approve a re-encryption path (R-15.9); key retirement: backup and point-in-time retention periods, no key destruction until legal hold exists, and Security plus Privacy Officer sign-off to destroy a key; run one pre-production key-rotation drill after the cut-off; whether an 835 or find-by-member-ID feature gets a tenant-keyed blind index.</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Shapes the Azure-cutover key rotation ADR and any member-ID matching feature.</t>
+        </is>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>An answer to each of the four (rotation path, key retirement policy, drill, blind index); the rotation parts can wait for the cutover ADR.</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1; R-7.3.4; R-15.9; docs/specs/field-encryption-aad.md</t>
+        </is>
+      </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1 AAD plan session 2026-09-28</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>Azure cutover</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="n"/>
+      <c r="L101" s="3" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>OA-104</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Decide whether rcm_claim_lines.account_number (the practice's patient account number in revenue-cycle files) is field-encrypted like member IDs.</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>HC-7.3/R-7.3.3 list only SSN, MBI, member IDs, and bank data, so plaintext breaks no MUST rule today; it is still an HC-1.1 identifier protected only by at-rest encryption and RLS.</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>Yes/no from the Security and Privacy Officers; if yes, the agent adds it to the ADR 0011 build.</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1; HC-1.1; HC-7.3; ADR 0011; docs/specs/field-encryption-aad.md</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>SC-B7.1 AAD plan session 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>Before the first real practice</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="n"/>
+      <c r="L102" s="3" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L97"/>
+  <autoFilter ref="A1:L102"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Action Items" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Action Items'!$A$1:$L$99</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5710,8 +5710,116 @@
       <c r="K97" s="3" t="n"/>
       <c r="L97" s="3" t="n"/>
     </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>OA-105</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Legal/Compliance</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>Decide with counsel whether appeal attachments (clinical records) may be disposed of after sending, keeping a manifest and hash, or must be kept for the appeal-record retention period.</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>HC-3.7 (ADR 0013) keeps them for the full appeal-record period until answered; affects storage of PHI in appeal packets (A5).</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>Counsel answer with citation (REQUIREMENTS §9.2, FL Rule 64B8-10.002, R-3.8.2).</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>HC-3.7; HC-10.1; §9.2; ADR 0013</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>PR #107 session 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>Before appeal attachments (A5)</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>OA-106</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>Approve PR #107 (ADR 0013 and HIPAA rules HC-3.5 to HC-3.9) in writing on the PR.</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>HC-13.2: an agent may not merge a change to HIPAA_COMPLIANCE.md without the owner's written approval in the PR.</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>A PR comment or approving review saying you approve.</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>HC-13.2; ADR 0013</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>PR #107 session 2026-09-29</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L97"/>
+  <autoFilter ref="A1:L99"/>
   <dataValidations count="3">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Blocked,Done,Dropped"</formula1>

--- a/docs/owner/OWNER_ACTION_ITEMS.xlsx
+++ b/docs/owner/OWNER_ACTION_ITEMS.xlsx
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -6086,7 +6086,11 @@
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr"/>
-      <c r="L104" s="3" t="inlineStr"/>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L104"/>
